--- a/artfynd/A 60117-2024 artfynd.xlsx
+++ b/artfynd/A 60117-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2158,10 +2158,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123988446</v>
+        <v>123989081</v>
       </c>
       <c r="B14" t="n">
-        <v>78788</v>
+        <v>90986</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2174,34 +2174,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460371</v>
+        <v>460222</v>
       </c>
       <c r="R14" t="n">
-        <v>7086703</v>
+        <v>7086704</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2260,10 +2260,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123989081</v>
+        <v>123988446</v>
       </c>
       <c r="B15" t="n">
-        <v>90986</v>
+        <v>78788</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2276,34 +2276,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460222</v>
+        <v>460371</v>
       </c>
       <c r="R15" t="n">
-        <v>7086704</v>
+        <v>7086703</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2566,7 +2566,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123988998</v>
+        <v>123988501</v>
       </c>
       <c r="B18" t="n">
         <v>78788</v>
@@ -2602,14 +2602,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>460216</v>
+        <v>460349</v>
       </c>
       <c r="R18" t="n">
-        <v>7086687</v>
+        <v>7086748</v>
       </c>
       <c r="S18" t="n">
         <v>9</v>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2703,7 +2703,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123988501</v>
+        <v>123988998</v>
       </c>
       <c r="B19" t="n">
         <v>78788</v>
@@ -2739,14 +2739,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>460349</v>
+        <v>460216</v>
       </c>
       <c r="R19" t="n">
-        <v>7086748</v>
+        <v>7086687</v>
       </c>
       <c r="S19" t="n">
         <v>9</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3633,6 +3633,1699 @@
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>124025461</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Häggsjövik V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>460078</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7086651</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>124025457</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Häggsjövik V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>460222</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7086760</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>124025476</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91008</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Häggsjövik V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>460154</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7086694</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>124025473</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91008</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Häggsjövik V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>460235</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7086681</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>124025465</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Häggsjövik V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>460240</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7086700</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>124025456</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Häggsjövik V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>460284</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7086765</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>124025470</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91683</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>67</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Sprickporing</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Diplomitoporus crustulinus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Häggsjövik V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>460140</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7086711</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>124025469</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Häggsjövik V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>460378</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7086700</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack Färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>124025467</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Häggsjövik V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>460343</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7086730</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>124025464</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Häggsjövik V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>460209</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7086674</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>124025475</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91008</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Häggsjövik V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>460284</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7086722</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>124025462</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Häggsjövik V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>460183</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7086654</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>124025459</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Häggsjövik V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>460150</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7086691</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>124025458</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Häggsjövik V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>460205</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7086746</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>124025453</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Häggsjövik V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>460668</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7086736</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>124025460</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Häggsjövik V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>460124</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7086694</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60117-2024 artfynd.xlsx
+++ b/artfynd/A 60117-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123991476</v>
+        <v>123988501</v>
       </c>
       <c r="B2" t="n">
         <v>78788</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460544</v>
+        <v>460349</v>
       </c>
       <c r="R2" t="n">
-        <v>7086749</v>
+        <v>7086748</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -817,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123988808</v>
+        <v>123988472</v>
       </c>
       <c r="B3" t="n">
-        <v>95313</v>
+        <v>91008</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,25 +824,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2809</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -857,13 +852,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460285</v>
+        <v>460371</v>
       </c>
       <c r="R3" t="n">
-        <v>7086685</v>
+        <v>7086703</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -919,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123991344</v>
+        <v>123987913</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,21 +930,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460415</v>
+        <v>460590</v>
       </c>
       <c r="R4" t="n">
-        <v>7086783</v>
+        <v>7086691</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,21 +987,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:36</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:36</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1015,51 +1000,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123989562</v>
+        <v>123990278</v>
       </c>
       <c r="B5" t="n">
-        <v>56692</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1072,39 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460190</v>
+        <v>460105</v>
       </c>
       <c r="R5" t="n">
-        <v>7086684</v>
+        <v>7086675</v>
       </c>
       <c r="S5" t="n">
         <v>8</v>
@@ -1136,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1146,12 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snötäcket i flerskiktad granskog.</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1166,6 +1116,26 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1183,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123988472</v>
+        <v>123991224</v>
       </c>
       <c r="B6" t="n">
-        <v>91008</v>
+        <v>57861</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1195,41 +1165,60 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460371</v>
+        <v>460332</v>
       </c>
       <c r="R6" t="n">
-        <v>7086703</v>
+        <v>7086777</v>
       </c>
       <c r="S6" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1256,11 +1245,21 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1269,23 +1268,28 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123987918</v>
+        <v>123988998</v>
       </c>
       <c r="B7" t="n">
         <v>78788</v>
@@ -1321,14 +1325,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460582</v>
+        <v>460216</v>
       </c>
       <c r="R7" t="n">
-        <v>7086692</v>
+        <v>7086687</v>
       </c>
       <c r="S7" t="n">
         <v>9</v>
@@ -1360,7 +1364,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1370,7 +1374,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1422,10 +1426,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123990224</v>
+        <v>123988915</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
+        <v>90986</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1438,34 +1442,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460370</v>
+        <v>460262</v>
       </c>
       <c r="R8" t="n">
-        <v>7086712</v>
+        <v>7086681</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1524,10 +1528,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123991224</v>
+        <v>123991344</v>
       </c>
       <c r="B9" t="n">
-        <v>57861</v>
+        <v>78788</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1536,60 +1540,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460332</v>
+        <v>460415</v>
       </c>
       <c r="R9" t="n">
-        <v>7086777</v>
+        <v>7086783</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1618,7 +1603,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1628,7 +1613,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1643,6 +1628,26 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1660,10 +1665,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123987913</v>
+        <v>123990830</v>
       </c>
       <c r="B10" t="n">
-        <v>90990</v>
+        <v>57491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1676,37 +1681,47 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460590</v>
+        <v>460249</v>
       </c>
       <c r="R10" t="n">
-        <v>7086691</v>
+        <v>7086743</v>
       </c>
       <c r="S10" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1733,11 +1748,26 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på en gran.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1746,26 +1776,51 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123991060</v>
+        <v>123990384</v>
       </c>
       <c r="B11" t="n">
-        <v>91008</v>
+        <v>57861</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1774,31 +1829,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1807,13 +1876,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460261</v>
+        <v>460150</v>
       </c>
       <c r="R11" t="n">
-        <v>7086790</v>
+        <v>7086698</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1842,7 +1911,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1852,7 +1921,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1867,26 +1936,6 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1904,7 +1953,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123989420</v>
+        <v>123988446</v>
       </c>
       <c r="B12" t="n">
         <v>78788</v>
@@ -1940,14 +1989,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>460223</v>
+        <v>460371</v>
       </c>
       <c r="R12" t="n">
-        <v>7086707</v>
+        <v>7086703</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -2006,10 +2055,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123990830</v>
+        <v>123988447</v>
       </c>
       <c r="B13" t="n">
-        <v>57491</v>
+        <v>57861</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2018,20 +2067,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2039,10 +2088,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2052,17 +2110,17 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460249</v>
+        <v>460385</v>
       </c>
       <c r="R13" t="n">
-        <v>7086743</v>
+        <v>7086719</v>
       </c>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2091,7 +2149,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2101,12 +2159,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på en gran.</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2121,26 +2174,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2158,10 +2191,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123989081</v>
+        <v>123988808</v>
       </c>
       <c r="B14" t="n">
-        <v>90986</v>
+        <v>95313</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2170,38 +2203,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>2809</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460222</v>
+        <v>460285</v>
       </c>
       <c r="R14" t="n">
-        <v>7086704</v>
+        <v>7086685</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2260,7 +2293,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123988446</v>
+        <v>123990849</v>
       </c>
       <c r="B15" t="n">
         <v>78788</v>
@@ -2296,17 +2329,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460371</v>
+        <v>460241</v>
       </c>
       <c r="R15" t="n">
-        <v>7086703</v>
+        <v>7086734</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2333,11 +2366,21 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2346,26 +2389,51 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123988915</v>
+        <v>123989420</v>
       </c>
       <c r="B16" t="n">
-        <v>90986</v>
+        <v>78788</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2378,21 +2446,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2402,10 +2470,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460262</v>
+        <v>460223</v>
       </c>
       <c r="R16" t="n">
-        <v>7086681</v>
+        <v>7086707</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2464,10 +2532,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123989913</v>
+        <v>123991060</v>
       </c>
       <c r="B17" t="n">
-        <v>78788</v>
+        <v>91008</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2480,37 +2548,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>460291</v>
+        <v>460261</v>
       </c>
       <c r="R17" t="n">
-        <v>7086773</v>
+        <v>7086790</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2537,11 +2610,21 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2550,23 +2633,48 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123988501</v>
+        <v>123990224</v>
       </c>
       <c r="B18" t="n">
         <v>78788</v>
@@ -2606,13 +2714,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>460349</v>
+        <v>460370</v>
       </c>
       <c r="R18" t="n">
-        <v>7086748</v>
+        <v>7086712</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2639,21 +2747,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2662,51 +2760,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123988998</v>
+        <v>123989562</v>
       </c>
       <c r="B19" t="n">
-        <v>78788</v>
+        <v>56692</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2719,37 +2792,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>460216</v>
+        <v>460190</v>
       </c>
       <c r="R19" t="n">
-        <v>7086687</v>
+        <v>7086684</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2778,7 +2856,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2788,7 +2866,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket i flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2803,26 +2886,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2840,10 +2903,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123990849</v>
+        <v>123989782</v>
       </c>
       <c r="B20" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2856,37 +2919,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>460241</v>
+        <v>460153</v>
       </c>
       <c r="R20" t="n">
-        <v>7086734</v>
+        <v>7086693</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2915,7 +2983,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2925,7 +2993,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en stående och en liggande död granstam.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2954,12 +3027,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2977,10 +3050,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123990384</v>
+        <v>123987918</v>
       </c>
       <c r="B21" t="n">
-        <v>57861</v>
+        <v>78788</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2989,60 +3062,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>460150</v>
+        <v>460582</v>
       </c>
       <c r="R21" t="n">
-        <v>7086698</v>
+        <v>7086692</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3071,7 +3125,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3081,7 +3135,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3096,6 +3150,26 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3113,10 +3187,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123988447</v>
+        <v>123991476</v>
       </c>
       <c r="B22" t="n">
-        <v>57861</v>
+        <v>78788</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3125,60 +3199,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>460385</v>
+        <v>460544</v>
       </c>
       <c r="R22" t="n">
-        <v>7086719</v>
+        <v>7086749</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3207,7 +3262,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3217,7 +3272,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3232,6 +3292,26 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3351,10 +3431,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123989782</v>
+        <v>123989081</v>
       </c>
       <c r="B24" t="n">
-        <v>57491</v>
+        <v>90986</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3367,42 +3447,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>460153</v>
+        <v>460222</v>
       </c>
       <c r="R24" t="n">
-        <v>7086693</v>
+        <v>7086704</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3429,26 +3504,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>09:52</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en stående och en liggande död granstam.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3457,48 +3517,23 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123990278</v>
+        <v>123989913</v>
       </c>
       <c r="B25" t="n">
         <v>78788</v>
@@ -3538,13 +3573,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>460105</v>
+        <v>460291</v>
       </c>
       <c r="R25" t="n">
-        <v>7086675</v>
+        <v>7086773</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3571,21 +3606,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3594,48 +3619,23 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124025461</v>
+        <v>124025462</v>
       </c>
       <c r="B26" t="n">
         <v>57491</v>
@@ -3675,10 +3675,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>460078</v>
+        <v>460183</v>
       </c>
       <c r="R26" t="n">
-        <v>7086651</v>
+        <v>7086654</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3742,7 +3742,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124025457</v>
+        <v>124025458</v>
       </c>
       <c r="B27" t="n">
         <v>57491</v>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>460222</v>
+        <v>460205</v>
       </c>
       <c r="R27" t="n">
-        <v>7086760</v>
+        <v>7086746</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3849,7 +3849,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124025476</v>
+        <v>124025475</v>
       </c>
       <c r="B28" t="n">
         <v>91008</v>
@@ -3889,10 +3889,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>460154</v>
+        <v>460284</v>
       </c>
       <c r="R28" t="n">
-        <v>7086694</v>
+        <v>7086722</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3933,7 +3933,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4054,7 +4053,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124025465</v>
+        <v>124025453</v>
       </c>
       <c r="B30" t="n">
         <v>57491</v>
@@ -4094,10 +4093,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>460240</v>
+        <v>460668</v>
       </c>
       <c r="R30" t="n">
-        <v>7086700</v>
+        <v>7086736</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4161,7 +4160,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124025456</v>
+        <v>124025467</v>
       </c>
       <c r="B31" t="n">
         <v>57491</v>
@@ -4201,10 +4200,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>460284</v>
+        <v>460343</v>
       </c>
       <c r="R31" t="n">
-        <v>7086765</v>
+        <v>7086730</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4268,10 +4267,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124025470</v>
+        <v>124025465</v>
       </c>
       <c r="B32" t="n">
-        <v>91683</v>
+        <v>57491</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4280,25 +4279,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4308,10 +4307,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>460140</v>
+        <v>460240</v>
       </c>
       <c r="R32" t="n">
-        <v>7086711</v>
+        <v>7086700</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4344,6 +4343,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4370,7 +4374,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124025469</v>
+        <v>124025459</v>
       </c>
       <c r="B33" t="n">
         <v>57491</v>
@@ -4410,10 +4414,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>460378</v>
+        <v>460150</v>
       </c>
       <c r="R33" t="n">
-        <v>7086700</v>
+        <v>7086691</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4450,7 +4454,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack Färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4477,7 +4481,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124025467</v>
+        <v>124025456</v>
       </c>
       <c r="B34" t="n">
         <v>57491</v>
@@ -4517,10 +4521,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>460343</v>
+        <v>460284</v>
       </c>
       <c r="R34" t="n">
-        <v>7086730</v>
+        <v>7086765</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4584,7 +4588,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124025464</v>
+        <v>124025460</v>
       </c>
       <c r="B35" t="n">
         <v>57491</v>
@@ -4624,10 +4628,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>460209</v>
+        <v>460124</v>
       </c>
       <c r="R35" t="n">
-        <v>7086674</v>
+        <v>7086694</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4691,10 +4695,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124025475</v>
+        <v>124025464</v>
       </c>
       <c r="B36" t="n">
-        <v>91008</v>
+        <v>57491</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4707,21 +4711,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4731,10 +4735,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>460284</v>
+        <v>460209</v>
       </c>
       <c r="R36" t="n">
-        <v>7086722</v>
+        <v>7086674</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4767,6 +4771,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4793,7 +4802,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124025462</v>
+        <v>124025457</v>
       </c>
       <c r="B37" t="n">
         <v>57491</v>
@@ -4833,10 +4842,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>460183</v>
+        <v>460222</v>
       </c>
       <c r="R37" t="n">
-        <v>7086654</v>
+        <v>7086760</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4873,7 +4882,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4900,7 +4909,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124025459</v>
+        <v>124025469</v>
       </c>
       <c r="B38" t="n">
         <v>57491</v>
@@ -4940,10 +4949,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>460150</v>
+        <v>460378</v>
       </c>
       <c r="R38" t="n">
-        <v>7086691</v>
+        <v>7086700</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4980,7 +4989,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack Färska och äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5007,10 +5016,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124025458</v>
+        <v>124025476</v>
       </c>
       <c r="B39" t="n">
-        <v>57491</v>
+        <v>91008</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5023,21 +5032,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5047,10 +5056,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>460205</v>
+        <v>460154</v>
       </c>
       <c r="R39" t="n">
-        <v>7086746</v>
+        <v>7086694</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5085,17 +5094,13 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5114,10 +5119,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124025453</v>
+        <v>124025470</v>
       </c>
       <c r="B40" t="n">
-        <v>57491</v>
+        <v>91683</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5126,25 +5131,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5154,10 +5159,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>460668</v>
+        <v>460140</v>
       </c>
       <c r="R40" t="n">
-        <v>7086736</v>
+        <v>7086711</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5190,11 +5195,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5221,7 +5221,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124025460</v>
+        <v>124025461</v>
       </c>
       <c r="B41" t="n">
         <v>57491</v>
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>460124</v>
+        <v>460078</v>
       </c>
       <c r="R41" t="n">
-        <v>7086694</v>
+        <v>7086651</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5301,7 +5301,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 60117-2024 artfynd.xlsx
+++ b/artfynd/A 60117-2024 artfynd.xlsx
@@ -1953,10 +1953,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123988446</v>
+        <v>123988447</v>
       </c>
       <c r="B12" t="n">
-        <v>78788</v>
+        <v>57861</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1965,38 +1965,57 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>460371</v>
+        <v>460385</v>
       </c>
       <c r="R12" t="n">
-        <v>7086703</v>
+        <v>7086719</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -2026,11 +2045,21 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2039,26 +2068,31 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123988447</v>
+        <v>123988446</v>
       </c>
       <c r="B13" t="n">
-        <v>57861</v>
+        <v>78788</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2067,57 +2101,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460385</v>
+        <v>460371</v>
       </c>
       <c r="R13" t="n">
-        <v>7086719</v>
+        <v>7086703</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2147,21 +2162,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2170,21 +2175,16 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 60117-2024 artfynd.xlsx
+++ b/artfynd/A 60117-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123988501</v>
+        <v>123990224</v>
       </c>
       <c r="B2" t="n">
         <v>78788</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460349</v>
+        <v>460370</v>
       </c>
       <c r="R2" t="n">
-        <v>7086748</v>
+        <v>7086712</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,21 +748,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,51 +761,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123988472</v>
+        <v>123990841</v>
       </c>
       <c r="B3" t="n">
-        <v>91008</v>
+        <v>57644</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460371</v>
+        <v>460642</v>
       </c>
       <c r="R3" t="n">
-        <v>7086703</v>
+        <v>7086699</v>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -914,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123987913</v>
+        <v>123991060</v>
       </c>
       <c r="B4" t="n">
-        <v>90990</v>
+        <v>91008</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,37 +895,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460590</v>
+        <v>460261</v>
       </c>
       <c r="R4" t="n">
-        <v>7086691</v>
+        <v>7086790</v>
       </c>
       <c r="S4" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,11 +957,21 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1000,23 +980,48 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123990278</v>
+        <v>123991344</v>
       </c>
       <c r="B5" t="n">
         <v>78788</v>
@@ -1052,17 +1057,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460105</v>
+        <v>460415</v>
       </c>
       <c r="R5" t="n">
-        <v>7086675</v>
+        <v>7086783</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,10 +1158,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123991224</v>
+        <v>123989081</v>
       </c>
       <c r="B6" t="n">
-        <v>57861</v>
+        <v>90986</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,60 +1170,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460332</v>
+        <v>460222</v>
       </c>
       <c r="R6" t="n">
-        <v>7086777</v>
+        <v>7086704</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1245,21 +1231,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1268,31 +1244,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123988998</v>
+        <v>123988472</v>
       </c>
       <c r="B7" t="n">
-        <v>78788</v>
+        <v>91008</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1305,37 +1276,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460216</v>
+        <v>460371</v>
       </c>
       <c r="R7" t="n">
-        <v>7086687</v>
+        <v>7086703</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1362,21 +1333,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1385,51 +1346,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123988915</v>
+        <v>123990830</v>
       </c>
       <c r="B8" t="n">
-        <v>90986</v>
+        <v>57491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1442,37 +1378,47 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460262</v>
+        <v>460249</v>
       </c>
       <c r="R8" t="n">
-        <v>7086681</v>
+        <v>7086743</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1499,11 +1445,26 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på en gran.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1512,23 +1473,48 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123991344</v>
+        <v>123990849</v>
       </c>
       <c r="B9" t="n">
         <v>78788</v>
@@ -1564,17 +1550,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460415</v>
+        <v>460241</v>
       </c>
       <c r="R9" t="n">
-        <v>7086783</v>
+        <v>7086734</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1603,7 +1589,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1613,7 +1599,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1665,10 +1651,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123990830</v>
+        <v>123987913</v>
       </c>
       <c r="B10" t="n">
-        <v>57491</v>
+        <v>90990</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1681,47 +1667,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460249</v>
+        <v>460590</v>
       </c>
       <c r="R10" t="n">
-        <v>7086743</v>
+        <v>7086691</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1748,26 +1724,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på en gran.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1776,51 +1737,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123990384</v>
+        <v>123988501</v>
       </c>
       <c r="B11" t="n">
-        <v>57861</v>
+        <v>78788</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1829,60 +1765,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460150</v>
+        <v>460349</v>
       </c>
       <c r="R11" t="n">
-        <v>7086698</v>
+        <v>7086748</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1911,7 +1828,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1921,7 +1838,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1936,6 +1853,26 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1953,10 +1890,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123988447</v>
+        <v>123989562</v>
       </c>
       <c r="B12" t="n">
-        <v>57861</v>
+        <v>56692</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1965,20 +1902,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1986,39 +1923,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>460385</v>
+        <v>460190</v>
       </c>
       <c r="R12" t="n">
-        <v>7086719</v>
+        <v>7086684</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2047,7 +1970,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2057,7 +1980,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket i flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2089,7 +2017,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123988446</v>
+        <v>123990278</v>
       </c>
       <c r="B13" t="n">
         <v>78788</v>
@@ -2125,17 +2053,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460371</v>
+        <v>460105</v>
       </c>
       <c r="R13" t="n">
-        <v>7086703</v>
+        <v>7086675</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2162,11 +2090,21 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2175,26 +2113,51 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123988808</v>
+        <v>123989913</v>
       </c>
       <c r="B14" t="n">
-        <v>95313</v>
+        <v>78788</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2203,38 +2166,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460285</v>
+        <v>460291</v>
       </c>
       <c r="R14" t="n">
-        <v>7086685</v>
+        <v>7086773</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2293,7 +2256,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123990849</v>
+        <v>123988446</v>
       </c>
       <c r="B15" t="n">
         <v>78788</v>
@@ -2329,17 +2292,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460241</v>
+        <v>460371</v>
       </c>
       <c r="R15" t="n">
-        <v>7086734</v>
+        <v>7086703</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2366,21 +2329,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2389,41 +2342,16 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2532,10 +2460,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123991060</v>
+        <v>123987918</v>
       </c>
       <c r="B17" t="n">
-        <v>91008</v>
+        <v>78788</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2548,42 +2476,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>460261</v>
+        <v>460582</v>
       </c>
       <c r="R17" t="n">
-        <v>7086790</v>
+        <v>7086692</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2612,7 +2535,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2622,7 +2545,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2651,12 +2574,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2674,10 +2597,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123990224</v>
+        <v>123989782</v>
       </c>
       <c r="B18" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2690,37 +2613,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>460370</v>
+        <v>460153</v>
       </c>
       <c r="R18" t="n">
-        <v>7086712</v>
+        <v>7086693</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2747,11 +2675,26 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en stående och en liggande död granstam.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2760,26 +2703,51 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123989562</v>
+        <v>123990384</v>
       </c>
       <c r="B19" t="n">
-        <v>56692</v>
+        <v>57861</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2788,20 +2756,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102612</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2809,10 +2777,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2821,13 +2803,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>460190</v>
+        <v>460150</v>
       </c>
       <c r="R19" t="n">
-        <v>7086684</v>
+        <v>7086698</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2856,7 +2838,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2866,12 +2848,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snötäcket i flerskiktad granskog.</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2903,10 +2880,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123989782</v>
+        <v>123988998</v>
       </c>
       <c r="B20" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2919,39 +2896,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>460153</v>
+        <v>460216</v>
       </c>
       <c r="R20" t="n">
-        <v>7086693</v>
+        <v>7086687</v>
       </c>
       <c r="S20" t="n">
         <v>9</v>
@@ -2983,7 +2955,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2993,12 +2965,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en stående och en liggande död granstam.</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3027,12 +2994,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3050,10 +3017,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123987918</v>
+        <v>123988915</v>
       </c>
       <c r="B21" t="n">
-        <v>78788</v>
+        <v>90986</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3066,37 +3033,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>460582</v>
+        <v>460262</v>
       </c>
       <c r="R21" t="n">
-        <v>7086692</v>
+        <v>7086681</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3123,21 +3090,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>09:02</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>09:02</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3146,51 +3103,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123991476</v>
+        <v>123991224</v>
       </c>
       <c r="B22" t="n">
-        <v>78788</v>
+        <v>57861</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3199,41 +3131,60 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>460544</v>
+        <v>460332</v>
       </c>
       <c r="R22" t="n">
-        <v>7086749</v>
+        <v>7086777</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3262,7 +3213,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3272,12 +3223,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3292,26 +3238,6 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3329,10 +3255,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123990841</v>
+        <v>123988808</v>
       </c>
       <c r="B23" t="n">
-        <v>57644</v>
+        <v>95313</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3341,41 +3267,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>2809</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>460642</v>
+        <v>460285</v>
       </c>
       <c r="R23" t="n">
-        <v>7086699</v>
+        <v>7086685</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3431,10 +3357,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123989081</v>
+        <v>123991476</v>
       </c>
       <c r="B24" t="n">
-        <v>90986</v>
+        <v>78788</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3447,37 +3373,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>460222</v>
+        <v>460544</v>
       </c>
       <c r="R24" t="n">
-        <v>7086704</v>
+        <v>7086749</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3504,11 +3430,26 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3517,26 +3458,51 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123989913</v>
+        <v>123988447</v>
       </c>
       <c r="B25" t="n">
-        <v>78788</v>
+        <v>57861</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3545,38 +3511,57 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>460291</v>
+        <v>460385</v>
       </c>
       <c r="R25" t="n">
-        <v>7086773</v>
+        <v>7086719</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3606,11 +3591,21 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3619,23 +3614,28 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124025462</v>
+        <v>124025461</v>
       </c>
       <c r="B26" t="n">
         <v>57491</v>
@@ -3675,10 +3675,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>460183</v>
+        <v>460078</v>
       </c>
       <c r="R26" t="n">
-        <v>7086654</v>
+        <v>7086651</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3742,10 +3742,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124025458</v>
+        <v>124025475</v>
       </c>
       <c r="B27" t="n">
-        <v>57491</v>
+        <v>91008</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3758,21 +3758,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>460205</v>
+        <v>460284</v>
       </c>
       <c r="R27" t="n">
-        <v>7086746</v>
+        <v>7086722</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3818,11 +3818,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3849,10 +3844,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124025475</v>
+        <v>124025459</v>
       </c>
       <c r="B28" t="n">
-        <v>91008</v>
+        <v>57491</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3865,21 +3860,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3889,10 +3884,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>460284</v>
+        <v>460150</v>
       </c>
       <c r="R28" t="n">
-        <v>7086722</v>
+        <v>7086691</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3925,6 +3920,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3951,10 +3951,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124025473</v>
+        <v>124025469</v>
       </c>
       <c r="B29" t="n">
-        <v>91008</v>
+        <v>57491</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3967,21 +3967,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3991,10 +3991,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>460235</v>
+        <v>460378</v>
       </c>
       <c r="R29" t="n">
-        <v>7086681</v>
+        <v>7086700</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4027,6 +4027,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack Färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4053,7 +4058,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124025453</v>
+        <v>124025458</v>
       </c>
       <c r="B30" t="n">
         <v>57491</v>
@@ -4093,10 +4098,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>460668</v>
+        <v>460205</v>
       </c>
       <c r="R30" t="n">
-        <v>7086736</v>
+        <v>7086746</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4160,7 +4165,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124025467</v>
+        <v>124025457</v>
       </c>
       <c r="B31" t="n">
         <v>57491</v>
@@ -4200,10 +4205,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>460343</v>
+        <v>460222</v>
       </c>
       <c r="R31" t="n">
-        <v>7086730</v>
+        <v>7086760</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4240,7 +4245,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4267,7 +4272,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124025465</v>
+        <v>124025462</v>
       </c>
       <c r="B32" t="n">
         <v>57491</v>
@@ -4307,10 +4312,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>460240</v>
+        <v>460183</v>
       </c>
       <c r="R32" t="n">
-        <v>7086700</v>
+        <v>7086654</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4374,10 +4379,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124025459</v>
+        <v>124025470</v>
       </c>
       <c r="B33" t="n">
-        <v>57491</v>
+        <v>91683</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4386,25 +4391,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4414,10 +4419,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>460150</v>
+        <v>460140</v>
       </c>
       <c r="R33" t="n">
-        <v>7086691</v>
+        <v>7086711</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4450,11 +4455,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4481,7 +4481,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124025456</v>
+        <v>124025464</v>
       </c>
       <c r="B34" t="n">
         <v>57491</v>
@@ -4521,10 +4521,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>460284</v>
+        <v>460209</v>
       </c>
       <c r="R34" t="n">
-        <v>7086765</v>
+        <v>7086674</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124025464</v>
+        <v>124025465</v>
       </c>
       <c r="B36" t="n">
         <v>57491</v>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>460209</v>
+        <v>460240</v>
       </c>
       <c r="R36" t="n">
-        <v>7086674</v>
+        <v>7086700</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4802,7 +4802,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124025457</v>
+        <v>124025456</v>
       </c>
       <c r="B37" t="n">
         <v>57491</v>
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>460222</v>
+        <v>460284</v>
       </c>
       <c r="R37" t="n">
-        <v>7086760</v>
+        <v>7086765</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4909,7 +4909,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124025469</v>
+        <v>124025467</v>
       </c>
       <c r="B38" t="n">
         <v>57491</v>
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>460378</v>
+        <v>460343</v>
       </c>
       <c r="R38" t="n">
-        <v>7086700</v>
+        <v>7086730</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4989,7 +4989,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack Färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5016,7 +5016,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124025476</v>
+        <v>124025473</v>
       </c>
       <c r="B39" t="n">
         <v>91008</v>
@@ -5056,10 +5056,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>460154</v>
+        <v>460235</v>
       </c>
       <c r="R39" t="n">
-        <v>7086694</v>
+        <v>7086681</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5100,7 +5100,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5119,10 +5118,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124025470</v>
+        <v>124025476</v>
       </c>
       <c r="B40" t="n">
-        <v>91683</v>
+        <v>91008</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5131,25 +5130,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>67</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5159,10 +5158,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>460140</v>
+        <v>460154</v>
       </c>
       <c r="R40" t="n">
-        <v>7086711</v>
+        <v>7086694</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5203,6 +5202,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5221,7 +5221,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124025461</v>
+        <v>124025453</v>
       </c>
       <c r="B41" t="n">
         <v>57491</v>
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>460078</v>
+        <v>460668</v>
       </c>
       <c r="R41" t="n">
-        <v>7086651</v>
+        <v>7086736</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5301,7 +5301,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 60117-2024 artfynd.xlsx
+++ b/artfynd/A 60117-2024 artfynd.xlsx
@@ -1362,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123990830</v>
+        <v>123990849</v>
       </c>
       <c r="B8" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,47 +1378,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460249</v>
+        <v>460241</v>
       </c>
       <c r="R8" t="n">
-        <v>7086743</v>
+        <v>7086734</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1447,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,12 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på en gran.</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,12 +1476,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1514,10 +1499,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123990849</v>
+        <v>123990830</v>
       </c>
       <c r="B9" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1530,37 +1515,47 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460241</v>
+        <v>460249</v>
       </c>
       <c r="R9" t="n">
-        <v>7086734</v>
+        <v>7086743</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1589,7 +1584,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1599,7 +1594,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1628,12 +1628,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -3357,10 +3357,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123991476</v>
+        <v>123988447</v>
       </c>
       <c r="B24" t="n">
-        <v>78788</v>
+        <v>57861</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3369,41 +3369,60 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>460544</v>
+        <v>460385</v>
       </c>
       <c r="R24" t="n">
-        <v>7086749</v>
+        <v>7086719</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3432,7 +3451,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3442,12 +3461,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3462,26 +3476,6 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3499,10 +3493,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123988447</v>
+        <v>123991476</v>
       </c>
       <c r="B25" t="n">
-        <v>57861</v>
+        <v>78788</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3511,60 +3505,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>460385</v>
+        <v>460544</v>
       </c>
       <c r="R25" t="n">
-        <v>7086719</v>
+        <v>7086749</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3593,7 +3568,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3603,7 +3578,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3618,6 +3598,26 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124025461</v>
+        <v>124025475</v>
       </c>
       <c r="B26" t="n">
-        <v>57491</v>
+        <v>91008</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3651,21 +3651,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3675,10 +3675,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>460078</v>
+        <v>460284</v>
       </c>
       <c r="R26" t="n">
-        <v>7086651</v>
+        <v>7086722</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3711,11 +3711,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3742,10 +3737,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124025475</v>
+        <v>124025461</v>
       </c>
       <c r="B27" t="n">
-        <v>91008</v>
+        <v>57491</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3758,21 +3753,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3782,10 +3777,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>460284</v>
+        <v>460078</v>
       </c>
       <c r="R27" t="n">
-        <v>7086722</v>
+        <v>7086651</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3818,6 +3813,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4909,10 +4909,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124025467</v>
+        <v>124025473</v>
       </c>
       <c r="B38" t="n">
-        <v>57491</v>
+        <v>91008</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4925,21 +4925,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>460343</v>
+        <v>460235</v>
       </c>
       <c r="R38" t="n">
-        <v>7086730</v>
+        <v>7086681</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4985,11 +4985,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5016,10 +5011,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124025473</v>
+        <v>124025467</v>
       </c>
       <c r="B39" t="n">
-        <v>91008</v>
+        <v>57491</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5032,21 +5027,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5056,10 +5051,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>460235</v>
+        <v>460343</v>
       </c>
       <c r="R39" t="n">
-        <v>7086681</v>
+        <v>7086730</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5092,6 +5087,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 60117-2024 artfynd.xlsx
+++ b/artfynd/A 60117-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123990224</v>
+        <v>123990278</v>
       </c>
       <c r="B2" t="n">
         <v>78788</v>
@@ -711,17 +711,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460370</v>
+        <v>460105</v>
       </c>
       <c r="R2" t="n">
-        <v>7086712</v>
+        <v>7086675</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,11 +748,21 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -761,26 +771,51 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123990841</v>
+        <v>123990224</v>
       </c>
       <c r="B3" t="n">
-        <v>57644</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +828,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460642</v>
+        <v>460370</v>
       </c>
       <c r="R3" t="n">
-        <v>7086699</v>
+        <v>7086712</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123991060</v>
+        <v>123989782</v>
       </c>
       <c r="B4" t="n">
-        <v>91008</v>
+        <v>57491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,27 +930,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -924,13 +959,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460261</v>
+        <v>460153</v>
       </c>
       <c r="R4" t="n">
-        <v>7086790</v>
+        <v>7086693</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +1004,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en stående och en liggande död granstam.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,7 +1061,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123991344</v>
+        <v>123990849</v>
       </c>
       <c r="B5" t="n">
         <v>78788</v>
@@ -1057,17 +1097,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460415</v>
+        <v>460241</v>
       </c>
       <c r="R5" t="n">
-        <v>7086783</v>
+        <v>7086734</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,7 +1136,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1146,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,10 +1198,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123989081</v>
+        <v>123990841</v>
       </c>
       <c r="B6" t="n">
-        <v>90986</v>
+        <v>57644</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,37 +1214,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460222</v>
+        <v>460642</v>
       </c>
       <c r="R6" t="n">
-        <v>7086704</v>
+        <v>7086699</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1260,7 +1300,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123988472</v>
+        <v>123991060</v>
       </c>
       <c r="B7" t="n">
         <v>91008</v>
@@ -1294,19 +1334,24 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460371</v>
+        <v>460261</v>
       </c>
       <c r="R7" t="n">
-        <v>7086703</v>
+        <v>7086790</v>
       </c>
       <c r="S7" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1333,11 +1378,21 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1346,26 +1401,51 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123990849</v>
+        <v>123988808</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
+        <v>95313</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,41 +1454,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460241</v>
+        <v>460285</v>
       </c>
       <c r="R8" t="n">
-        <v>7086734</v>
+        <v>7086685</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1435,21 +1515,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1458,51 +1528,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123990830</v>
+        <v>123989081</v>
       </c>
       <c r="B9" t="n">
-        <v>57491</v>
+        <v>90986</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1515,47 +1560,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460249</v>
+        <v>460222</v>
       </c>
       <c r="R9" t="n">
-        <v>7086743</v>
+        <v>7086704</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1582,26 +1617,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på en gran.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1610,51 +1630,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123987913</v>
+        <v>123988472</v>
       </c>
       <c r="B10" t="n">
-        <v>90990</v>
+        <v>91008</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1667,21 +1662,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1691,10 +1686,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460590</v>
+        <v>460371</v>
       </c>
       <c r="R10" t="n">
-        <v>7086691</v>
+        <v>7086703</v>
       </c>
       <c r="S10" t="n">
         <v>30</v>
@@ -1753,7 +1748,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123988501</v>
+        <v>123991476</v>
       </c>
       <c r="B11" t="n">
         <v>78788</v>
@@ -1793,13 +1788,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460349</v>
+        <v>460544</v>
       </c>
       <c r="R11" t="n">
-        <v>7086748</v>
+        <v>7086749</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1828,7 +1823,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1838,7 +1833,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1890,10 +1890,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123989562</v>
+        <v>123990830</v>
       </c>
       <c r="B12" t="n">
-        <v>56692</v>
+        <v>57491</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1906,16 +1906,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1926,7 +1926,12 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1935,13 +1940,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>460190</v>
+        <v>460249</v>
       </c>
       <c r="R12" t="n">
-        <v>7086684</v>
+        <v>7086743</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1970,7 +1975,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1980,12 +1985,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket i flerskiktad granskog.</t>
+          <t>Färska och äldre ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2000,6 +2005,26 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2017,10 +2042,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123990278</v>
+        <v>123988915</v>
       </c>
       <c r="B13" t="n">
-        <v>78788</v>
+        <v>90986</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2033,21 +2058,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2057,13 +2082,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460105</v>
+        <v>460262</v>
       </c>
       <c r="R13" t="n">
-        <v>7086675</v>
+        <v>7086681</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2090,21 +2115,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2113,51 +2128,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123989913</v>
+        <v>123990384</v>
       </c>
       <c r="B14" t="n">
-        <v>78788</v>
+        <v>57861</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2166,41 +2156,60 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460291</v>
+        <v>460150</v>
       </c>
       <c r="R14" t="n">
-        <v>7086773</v>
+        <v>7086698</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2227,11 +2236,21 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2240,26 +2259,31 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123988446</v>
+        <v>123988447</v>
       </c>
       <c r="B15" t="n">
-        <v>78788</v>
+        <v>57861</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2268,38 +2292,57 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460371</v>
+        <v>460385</v>
       </c>
       <c r="R15" t="n">
-        <v>7086703</v>
+        <v>7086719</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2329,11 +2372,21 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2342,23 +2395,28 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123989420</v>
+        <v>123991344</v>
       </c>
       <c r="B16" t="n">
         <v>78788</v>
@@ -2394,17 +2452,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460223</v>
+        <v>460415</v>
       </c>
       <c r="R16" t="n">
-        <v>7086707</v>
+        <v>7086783</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2431,11 +2489,21 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2444,23 +2512,48 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123987918</v>
+        <v>123988998</v>
       </c>
       <c r="B17" t="n">
         <v>78788</v>
@@ -2496,14 +2589,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>460582</v>
+        <v>460216</v>
       </c>
       <c r="R17" t="n">
-        <v>7086692</v>
+        <v>7086687</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
@@ -2535,7 +2628,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2545,7 +2638,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2597,10 +2690,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123989782</v>
+        <v>123987918</v>
       </c>
       <c r="B18" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2613,39 +2706,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>460153</v>
+        <v>460582</v>
       </c>
       <c r="R18" t="n">
-        <v>7086693</v>
+        <v>7086692</v>
       </c>
       <c r="S18" t="n">
         <v>9</v>
@@ -2677,7 +2765,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2687,12 +2775,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en stående och en liggande död granstam.</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2721,12 +2804,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2744,10 +2827,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123990384</v>
+        <v>123988501</v>
       </c>
       <c r="B19" t="n">
-        <v>57861</v>
+        <v>78788</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2756,60 +2839,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>460150</v>
+        <v>460349</v>
       </c>
       <c r="R19" t="n">
-        <v>7086698</v>
+        <v>7086748</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2838,7 +2902,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2848,7 +2912,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2863,6 +2927,26 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2880,10 +2964,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123988998</v>
+        <v>123991224</v>
       </c>
       <c r="B20" t="n">
-        <v>78788</v>
+        <v>57861</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2892,41 +2976,60 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>460216</v>
+        <v>460332</v>
       </c>
       <c r="R20" t="n">
-        <v>7086687</v>
+        <v>7086777</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2955,7 +3058,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2965,7 +3068,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2980,26 +3083,6 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3017,10 +3100,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123988915</v>
+        <v>123989562</v>
       </c>
       <c r="B21" t="n">
-        <v>90986</v>
+        <v>56692</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3033,37 +3116,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>460262</v>
+        <v>460190</v>
       </c>
       <c r="R21" t="n">
-        <v>7086681</v>
+        <v>7086684</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3090,11 +3178,26 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket i flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3103,26 +3206,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123991224</v>
+        <v>123987913</v>
       </c>
       <c r="B22" t="n">
-        <v>57861</v>
+        <v>90990</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3131,60 +3239,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>460332</v>
+        <v>460590</v>
       </c>
       <c r="R22" t="n">
-        <v>7086777</v>
+        <v>7086691</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3211,21 +3300,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3234,31 +3313,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123988808</v>
+        <v>123989913</v>
       </c>
       <c r="B23" t="n">
-        <v>95313</v>
+        <v>78788</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3267,38 +3341,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>460285</v>
+        <v>460291</v>
       </c>
       <c r="R23" t="n">
-        <v>7086685</v>
+        <v>7086773</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3357,10 +3431,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123988447</v>
+        <v>123988446</v>
       </c>
       <c r="B24" t="n">
-        <v>57861</v>
+        <v>78788</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3369,57 +3443,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>460385</v>
+        <v>460371</v>
       </c>
       <c r="R24" t="n">
-        <v>7086719</v>
+        <v>7086703</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3449,21 +3504,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3472,28 +3517,23 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123991476</v>
+        <v>123989420</v>
       </c>
       <c r="B25" t="n">
         <v>78788</v>
@@ -3529,17 +3569,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>460544</v>
+        <v>460223</v>
       </c>
       <c r="R25" t="n">
-        <v>7086749</v>
+        <v>7086707</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3566,26 +3606,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3594,51 +3619,26 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124025475</v>
+        <v>124025462</v>
       </c>
       <c r="B26" t="n">
-        <v>91008</v>
+        <v>57491</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3651,21 +3651,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3675,10 +3675,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>460284</v>
+        <v>460183</v>
       </c>
       <c r="R26" t="n">
-        <v>7086722</v>
+        <v>7086654</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3711,6 +3711,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3737,7 +3742,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124025461</v>
+        <v>124025465</v>
       </c>
       <c r="B27" t="n">
         <v>57491</v>
@@ -3777,10 +3782,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>460078</v>
+        <v>460240</v>
       </c>
       <c r="R27" t="n">
-        <v>7086651</v>
+        <v>7086700</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3817,7 +3822,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3844,7 +3849,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124025459</v>
+        <v>124025460</v>
       </c>
       <c r="B28" t="n">
         <v>57491</v>
@@ -3884,10 +3889,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>460150</v>
+        <v>460124</v>
       </c>
       <c r="R28" t="n">
-        <v>7086691</v>
+        <v>7086694</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3951,7 +3956,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124025469</v>
+        <v>124025453</v>
       </c>
       <c r="B29" t="n">
         <v>57491</v>
@@ -3991,10 +3996,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>460378</v>
+        <v>460668</v>
       </c>
       <c r="R29" t="n">
-        <v>7086700</v>
+        <v>7086736</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4031,7 +4036,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack Färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4058,10 +4063,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124025458</v>
+        <v>124025475</v>
       </c>
       <c r="B30" t="n">
-        <v>57491</v>
+        <v>91008</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4074,21 +4079,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4098,10 +4103,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>460205</v>
+        <v>460284</v>
       </c>
       <c r="R30" t="n">
-        <v>7086746</v>
+        <v>7086722</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4134,11 +4139,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4165,7 +4165,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124025457</v>
+        <v>124025467</v>
       </c>
       <c r="B31" t="n">
         <v>57491</v>
@@ -4205,10 +4205,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>460222</v>
+        <v>460343</v>
       </c>
       <c r="R31" t="n">
-        <v>7086760</v>
+        <v>7086730</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4272,10 +4272,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124025462</v>
+        <v>124025473</v>
       </c>
       <c r="B32" t="n">
-        <v>57491</v>
+        <v>91008</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4288,21 +4288,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>460183</v>
+        <v>460235</v>
       </c>
       <c r="R32" t="n">
-        <v>7086654</v>
+        <v>7086681</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4348,11 +4348,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4379,10 +4374,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124025470</v>
+        <v>124025459</v>
       </c>
       <c r="B33" t="n">
-        <v>91683</v>
+        <v>57491</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4391,25 +4386,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4419,10 +4414,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>460140</v>
+        <v>460150</v>
       </c>
       <c r="R33" t="n">
-        <v>7086711</v>
+        <v>7086691</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4455,6 +4450,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4481,7 +4481,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124025464</v>
+        <v>124025457</v>
       </c>
       <c r="B34" t="n">
         <v>57491</v>
@@ -4521,10 +4521,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>460209</v>
+        <v>460222</v>
       </c>
       <c r="R34" t="n">
-        <v>7086674</v>
+        <v>7086760</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4588,7 +4588,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124025460</v>
+        <v>124025469</v>
       </c>
       <c r="B35" t="n">
         <v>57491</v>
@@ -4628,10 +4628,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>460124</v>
+        <v>460378</v>
       </c>
       <c r="R35" t="n">
-        <v>7086694</v>
+        <v>7086700</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack Färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4695,7 +4695,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124025465</v>
+        <v>124025458</v>
       </c>
       <c r="B36" t="n">
         <v>57491</v>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>460240</v>
+        <v>460205</v>
       </c>
       <c r="R36" t="n">
-        <v>7086700</v>
+        <v>7086746</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4802,10 +4802,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124025456</v>
+        <v>124025470</v>
       </c>
       <c r="B37" t="n">
-        <v>57491</v>
+        <v>91683</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4814,25 +4814,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>460284</v>
+        <v>460140</v>
       </c>
       <c r="R37" t="n">
-        <v>7086765</v>
+        <v>7086711</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4878,11 +4878,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4909,10 +4904,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124025473</v>
+        <v>124025464</v>
       </c>
       <c r="B38" t="n">
-        <v>91008</v>
+        <v>57491</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4925,21 +4920,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4949,10 +4944,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>460235</v>
+        <v>460209</v>
       </c>
       <c r="R38" t="n">
-        <v>7086681</v>
+        <v>7086674</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4985,6 +4980,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5011,7 +5011,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124025467</v>
+        <v>124025456</v>
       </c>
       <c r="B39" t="n">
         <v>57491</v>
@@ -5051,10 +5051,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>460343</v>
+        <v>460284</v>
       </c>
       <c r="R39" t="n">
-        <v>7086730</v>
+        <v>7086765</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5118,10 +5118,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124025476</v>
+        <v>124025461</v>
       </c>
       <c r="B40" t="n">
-        <v>91008</v>
+        <v>57491</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5134,21 +5134,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5158,10 +5158,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>460154</v>
+        <v>460078</v>
       </c>
       <c r="R40" t="n">
-        <v>7086694</v>
+        <v>7086651</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5196,13 +5196,17 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5221,10 +5225,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124025453</v>
+        <v>124025476</v>
       </c>
       <c r="B41" t="n">
-        <v>57491</v>
+        <v>91008</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5237,21 +5241,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5261,10 +5265,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>460668</v>
+        <v>460154</v>
       </c>
       <c r="R41" t="n">
-        <v>7086736</v>
+        <v>7086694</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5299,17 +5303,13 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60117-2024 artfynd.xlsx
+++ b/artfynd/A 60117-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123990830</v>
+        <v>123988501</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,47 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460249</v>
+        <v>460349</v>
       </c>
       <c r="R2" t="n">
-        <v>7086743</v>
+        <v>7086748</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -770,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på en gran.</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,12 +789,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -827,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123990278</v>
+        <v>123988808</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>95335</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -839,41 +824,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460105</v>
+        <v>460285</v>
       </c>
       <c r="R3" t="n">
-        <v>7086675</v>
+        <v>7086685</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -900,21 +885,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -923,48 +898,23 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123989420</v>
+        <v>123987918</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -1000,17 +950,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460223</v>
+        <v>460582</v>
       </c>
       <c r="R4" t="n">
-        <v>7086707</v>
+        <v>7086692</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1037,11 +987,21 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1050,26 +1010,51 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123989913</v>
+        <v>123988447</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1078,38 +1063,57 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460291</v>
+        <v>460385</v>
       </c>
       <c r="R5" t="n">
-        <v>7086773</v>
+        <v>7086719</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1139,11 +1143,21 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1152,26 +1166,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123988447</v>
+        <v>123991060</v>
       </c>
       <c r="B6" t="n">
-        <v>57883</v>
+        <v>91030</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1180,60 +1199,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460385</v>
+        <v>460261</v>
       </c>
       <c r="R6" t="n">
-        <v>7086719</v>
+        <v>7086790</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1262,7 +1267,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1272,7 +1277,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,6 +1292,26 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1304,10 +1329,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123991476</v>
+        <v>123991224</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1316,41 +1341,60 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460544</v>
+        <v>460332</v>
       </c>
       <c r="R7" t="n">
-        <v>7086749</v>
+        <v>7086777</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1379,7 +1423,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1389,12 +1433,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1409,26 +1448,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1446,10 +1465,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123987913</v>
+        <v>123990830</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1462,37 +1481,47 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460590</v>
+        <v>460249</v>
       </c>
       <c r="R8" t="n">
-        <v>7086691</v>
+        <v>7086743</v>
       </c>
       <c r="S8" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1519,11 +1548,26 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på en gran.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1532,26 +1576,51 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123989081</v>
+        <v>123990841</v>
       </c>
       <c r="B9" t="n">
-        <v>91008</v>
+        <v>57666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1564,37 +1633,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460222</v>
+        <v>460642</v>
       </c>
       <c r="R9" t="n">
-        <v>7086704</v>
+        <v>7086699</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1650,10 +1719,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123991060</v>
+        <v>123989562</v>
       </c>
       <c r="B10" t="n">
-        <v>91030</v>
+        <v>56714</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1666,27 +1735,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1695,13 +1764,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460261</v>
+        <v>460190</v>
       </c>
       <c r="R10" t="n">
-        <v>7086790</v>
+        <v>7086684</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1730,7 +1799,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1740,7 +1809,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket i flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1755,26 +1829,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1792,10 +1846,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123988446</v>
+        <v>123989782</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1808,37 +1862,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460371</v>
+        <v>460153</v>
       </c>
       <c r="R11" t="n">
-        <v>7086703</v>
+        <v>7086693</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1865,11 +1924,26 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en stående och en liggande död granstam.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1878,26 +1952,51 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123990841</v>
+        <v>123990849</v>
       </c>
       <c r="B12" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1910,37 +2009,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>460642</v>
+        <v>460241</v>
       </c>
       <c r="R12" t="n">
-        <v>7086699</v>
+        <v>7086734</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1967,11 +2066,21 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1980,23 +2089,48 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123990224</v>
+        <v>123991476</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -2036,13 +2170,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460370</v>
+        <v>460544</v>
       </c>
       <c r="R13" t="n">
-        <v>7086712</v>
+        <v>7086749</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2069,11 +2203,26 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2082,23 +2231,48 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123987918</v>
+        <v>123988446</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -2138,13 +2312,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460582</v>
+        <v>460371</v>
       </c>
       <c r="R14" t="n">
-        <v>7086692</v>
+        <v>7086703</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2171,21 +2345,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>09:02</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>09:02</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2194,51 +2358,26 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123989782</v>
+        <v>123990278</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2251,42 +2390,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460153</v>
+        <v>460105</v>
       </c>
       <c r="R15" t="n">
-        <v>7086693</v>
+        <v>7086675</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2315,7 +2449,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2325,12 +2459,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en stående och en liggande död granstam.</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2359,12 +2488,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2382,10 +2511,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123988808</v>
+        <v>123991344</v>
       </c>
       <c r="B16" t="n">
-        <v>95335</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2394,25 +2523,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2422,13 +2551,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460285</v>
+        <v>460415</v>
       </c>
       <c r="R16" t="n">
-        <v>7086685</v>
+        <v>7086783</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2455,11 +2584,21 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2468,26 +2607,51 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123988472</v>
+        <v>123987913</v>
       </c>
       <c r="B17" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2500,21 +2664,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2524,10 +2688,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>460371</v>
+        <v>460590</v>
       </c>
       <c r="R17" t="n">
-        <v>7086703</v>
+        <v>7086691</v>
       </c>
       <c r="S17" t="n">
         <v>30</v>
@@ -2586,10 +2750,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123990384</v>
+        <v>123988472</v>
       </c>
       <c r="B18" t="n">
-        <v>57883</v>
+        <v>91030</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2598,60 +2762,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>460150</v>
+        <v>460371</v>
       </c>
       <c r="R18" t="n">
-        <v>7086698</v>
+        <v>7086703</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2678,21 +2823,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:08</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>10:08</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2701,31 +2836,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123988915</v>
+        <v>123989420</v>
       </c>
       <c r="B19" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2738,21 +2868,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2762,10 +2892,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>460262</v>
+        <v>460223</v>
       </c>
       <c r="R19" t="n">
-        <v>7086681</v>
+        <v>7086707</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2824,7 +2954,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123990849</v>
+        <v>123990224</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2860,17 +2990,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>460241</v>
+        <v>460370</v>
       </c>
       <c r="R20" t="n">
-        <v>7086734</v>
+        <v>7086712</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2897,21 +3027,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2920,51 +3040,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123988998</v>
+        <v>123989081</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2977,21 +3072,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3001,13 +3096,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>460216</v>
+        <v>460222</v>
       </c>
       <c r="R21" t="n">
-        <v>7086687</v>
+        <v>7086704</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3034,21 +3129,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3057,51 +3142,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123991344</v>
+        <v>123990384</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3110,41 +3170,60 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>460415</v>
+        <v>460150</v>
       </c>
       <c r="R22" t="n">
-        <v>7086783</v>
+        <v>7086698</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3173,7 +3252,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3183,7 +3262,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3198,26 +3277,6 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3235,10 +3294,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123989562</v>
+        <v>123988998</v>
       </c>
       <c r="B23" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3251,42 +3310,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>460190</v>
+        <v>460216</v>
       </c>
       <c r="R23" t="n">
-        <v>7086684</v>
+        <v>7086687</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3315,7 +3369,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3325,12 +3379,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snötäcket i flerskiktad granskog.</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3345,6 +3394,26 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3362,10 +3431,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123988501</v>
+        <v>123988915</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3378,37 +3447,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>460349</v>
+        <v>460262</v>
       </c>
       <c r="R24" t="n">
-        <v>7086748</v>
+        <v>7086681</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3435,21 +3504,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3458,51 +3517,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123991224</v>
+        <v>123989913</v>
       </c>
       <c r="B25" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3511,60 +3545,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>460332</v>
+        <v>460291</v>
       </c>
       <c r="R25" t="n">
-        <v>7086777</v>
+        <v>7086773</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3591,21 +3606,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3614,31 +3619,26 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124025464</v>
+        <v>124025475</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3651,21 +3651,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3675,10 +3675,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>460209</v>
+        <v>460284</v>
       </c>
       <c r="R26" t="n">
-        <v>7086674</v>
+        <v>7086722</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3711,11 +3711,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3742,10 +3737,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124025459</v>
+        <v>124025470</v>
       </c>
       <c r="B27" t="n">
-        <v>57513</v>
+        <v>91705</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3754,25 +3749,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3782,10 +3777,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>460150</v>
+        <v>460140</v>
       </c>
       <c r="R27" t="n">
-        <v>7086691</v>
+        <v>7086711</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3818,11 +3813,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3849,10 +3839,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124025475</v>
+        <v>124025458</v>
       </c>
       <c r="B28" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3865,21 +3855,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3889,10 +3879,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>460284</v>
+        <v>460205</v>
       </c>
       <c r="R28" t="n">
-        <v>7086722</v>
+        <v>7086746</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3925,6 +3915,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3951,7 +3946,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124025456</v>
+        <v>124025469</v>
       </c>
       <c r="B29" t="n">
         <v>57513</v>
@@ -3991,10 +3986,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>460284</v>
+        <v>460378</v>
       </c>
       <c r="R29" t="n">
-        <v>7086765</v>
+        <v>7086700</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4031,7 +4026,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack Färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4058,7 +4053,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124025457</v>
+        <v>124025465</v>
       </c>
       <c r="B30" t="n">
         <v>57513</v>
@@ -4098,10 +4093,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>460222</v>
+        <v>460240</v>
       </c>
       <c r="R30" t="n">
-        <v>7086760</v>
+        <v>7086700</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4138,7 +4133,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4165,7 +4160,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124025465</v>
+        <v>124025462</v>
       </c>
       <c r="B31" t="n">
         <v>57513</v>
@@ -4205,10 +4200,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>460240</v>
+        <v>460183</v>
       </c>
       <c r="R31" t="n">
-        <v>7086700</v>
+        <v>7086654</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4379,10 +4374,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124025458</v>
+        <v>124025476</v>
       </c>
       <c r="B33" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4395,21 +4390,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4419,10 +4414,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>460205</v>
+        <v>460154</v>
       </c>
       <c r="R33" t="n">
-        <v>7086746</v>
+        <v>7086694</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4457,17 +4452,13 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4486,7 +4477,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124025462</v>
+        <v>124025453</v>
       </c>
       <c r="B34" t="n">
         <v>57513</v>
@@ -4526,10 +4517,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>460183</v>
+        <v>460668</v>
       </c>
       <c r="R34" t="n">
-        <v>7086654</v>
+        <v>7086736</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4593,10 +4584,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124025473</v>
+        <v>124025467</v>
       </c>
       <c r="B35" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4609,21 +4600,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4633,10 +4624,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>460235</v>
+        <v>460343</v>
       </c>
       <c r="R35" t="n">
-        <v>7086681</v>
+        <v>7086730</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4669,6 +4660,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4695,7 +4691,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124025467</v>
+        <v>124025459</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -4735,10 +4731,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>460343</v>
+        <v>460150</v>
       </c>
       <c r="R36" t="n">
-        <v>7086730</v>
+        <v>7086691</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4802,7 +4798,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124025461</v>
+        <v>124025456</v>
       </c>
       <c r="B37" t="n">
         <v>57513</v>
@@ -4842,10 +4838,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>460078</v>
+        <v>460284</v>
       </c>
       <c r="R37" t="n">
-        <v>7086651</v>
+        <v>7086765</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4882,7 +4878,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4909,7 +4905,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124025453</v>
+        <v>124025464</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -4949,10 +4945,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>460668</v>
+        <v>460209</v>
       </c>
       <c r="R38" t="n">
-        <v>7086736</v>
+        <v>7086674</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5016,10 +5012,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124025469</v>
+        <v>124025473</v>
       </c>
       <c r="B39" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5032,21 +5028,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5056,10 +5052,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>460378</v>
+        <v>460235</v>
       </c>
       <c r="R39" t="n">
-        <v>7086700</v>
+        <v>7086681</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5092,11 +5088,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack Färska och äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5123,10 +5114,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124025476</v>
+        <v>124025461</v>
       </c>
       <c r="B40" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5139,21 +5130,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5163,10 +5154,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>460154</v>
+        <v>460078</v>
       </c>
       <c r="R40" t="n">
-        <v>7086694</v>
+        <v>7086651</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5201,13 +5192,17 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5226,10 +5221,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124025470</v>
+        <v>124025457</v>
       </c>
       <c r="B41" t="n">
-        <v>91705</v>
+        <v>57513</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5238,25 +5233,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5266,10 +5261,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>460140</v>
+        <v>460222</v>
       </c>
       <c r="R41" t="n">
-        <v>7086711</v>
+        <v>7086760</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5302,6 +5297,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 60117-2024 artfynd.xlsx
+++ b/artfynd/A 60117-2024 artfynd.xlsx
@@ -812,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123988808</v>
+        <v>123988446</v>
       </c>
       <c r="B3" t="n">
-        <v>95335</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -824,25 +824,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460285</v>
+        <v>460371</v>
       </c>
       <c r="R3" t="n">
-        <v>7086685</v>
+        <v>7086703</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123987918</v>
+        <v>123990841</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,37 +930,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460582</v>
+        <v>460642</v>
       </c>
       <c r="R4" t="n">
-        <v>7086692</v>
+        <v>7086699</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,21 +987,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:02</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:02</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1010,51 +1000,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123988447</v>
+        <v>123989913</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,57 +1028,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460385</v>
+        <v>460291</v>
       </c>
       <c r="R5" t="n">
-        <v>7086719</v>
+        <v>7086773</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1143,21 +1089,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1166,31 +1102,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123991060</v>
+        <v>123989562</v>
       </c>
       <c r="B6" t="n">
-        <v>91030</v>
+        <v>56714</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1203,27 +1134,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1232,13 +1163,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460261</v>
+        <v>460190</v>
       </c>
       <c r="R6" t="n">
-        <v>7086790</v>
+        <v>7086684</v>
       </c>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1267,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1277,7 +1208,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket i flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1292,26 +1228,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1329,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123991224</v>
+        <v>123988808</v>
       </c>
       <c r="B7" t="n">
-        <v>57883</v>
+        <v>95335</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1345,56 +1261,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>2809</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460332</v>
+        <v>460285</v>
       </c>
       <c r="R7" t="n">
-        <v>7086777</v>
+        <v>7086685</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1421,21 +1318,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1444,31 +1331,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123990830</v>
+        <v>123991344</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1481,47 +1363,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460249</v>
+        <v>460415</v>
       </c>
       <c r="R8" t="n">
-        <v>7086743</v>
+        <v>7086783</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1550,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1560,12 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på en gran.</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1594,12 +1461,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1617,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123990841</v>
+        <v>123989782</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1633,37 +1500,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460642</v>
+        <v>460153</v>
       </c>
       <c r="R9" t="n">
-        <v>7086699</v>
+        <v>7086693</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1690,11 +1562,26 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en stående och en liggande död granstam.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1703,26 +1590,51 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123989562</v>
+        <v>123990830</v>
       </c>
       <c r="B10" t="n">
-        <v>56714</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1735,16 +1647,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1755,7 +1667,12 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1764,13 +1681,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460190</v>
+        <v>460249</v>
       </c>
       <c r="R10" t="n">
-        <v>7086684</v>
+        <v>7086743</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1799,7 +1716,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1809,12 +1726,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färsk spillning ovanpå snötäcket i flerskiktad granskog.</t>
+          <t>Färska och äldre ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1829,6 +1746,26 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1846,10 +1783,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123989782</v>
+        <v>123990224</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1862,42 +1799,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460153</v>
+        <v>460370</v>
       </c>
       <c r="R11" t="n">
-        <v>7086693</v>
+        <v>7086712</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1924,26 +1856,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:52</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en stående och en liggande död granstam.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1952,51 +1869,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123990849</v>
+        <v>123987913</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2009,37 +1901,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>460241</v>
+        <v>460590</v>
       </c>
       <c r="R12" t="n">
-        <v>7086734</v>
+        <v>7086691</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2066,21 +1958,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2089,51 +1971,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123991476</v>
+        <v>123989081</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2146,37 +2003,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460544</v>
+        <v>460222</v>
       </c>
       <c r="R13" t="n">
-        <v>7086749</v>
+        <v>7086704</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2203,26 +2060,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2231,51 +2073,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123988446</v>
+        <v>123988915</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2288,34 +2105,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460371</v>
+        <v>460262</v>
       </c>
       <c r="R14" t="n">
-        <v>7086703</v>
+        <v>7086681</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2374,7 +2191,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123990278</v>
+        <v>123988998</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2414,13 +2231,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460105</v>
+        <v>460216</v>
       </c>
       <c r="R15" t="n">
-        <v>7086675</v>
+        <v>7086687</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2449,7 +2266,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2459,7 +2276,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2511,7 +2328,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123991344</v>
+        <v>123990278</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2547,17 +2364,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460415</v>
+        <v>460105</v>
       </c>
       <c r="R16" t="n">
-        <v>7086783</v>
+        <v>7086675</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2586,7 +2403,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2596,7 +2413,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2648,10 +2465,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123987913</v>
+        <v>123988472</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2664,21 +2481,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2688,10 +2505,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>460590</v>
+        <v>460371</v>
       </c>
       <c r="R17" t="n">
-        <v>7086691</v>
+        <v>7086703</v>
       </c>
       <c r="S17" t="n">
         <v>30</v>
@@ -2750,10 +2567,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123988472</v>
+        <v>123987918</v>
       </c>
       <c r="B18" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2766,21 +2583,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2790,13 +2607,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>460371</v>
+        <v>460582</v>
       </c>
       <c r="R18" t="n">
-        <v>7086703</v>
+        <v>7086692</v>
       </c>
       <c r="S18" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2823,11 +2640,21 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2836,26 +2663,51 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123989420</v>
+        <v>123991060</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2868,37 +2720,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>460223</v>
+        <v>460261</v>
       </c>
       <c r="R19" t="n">
-        <v>7086707</v>
+        <v>7086790</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2925,11 +2782,21 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2938,23 +2805,48 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123990224</v>
+        <v>123990849</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2990,17 +2882,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>460370</v>
+        <v>460241</v>
       </c>
       <c r="R20" t="n">
-        <v>7086712</v>
+        <v>7086734</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3027,11 +2919,21 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3040,26 +2942,51 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123989081</v>
+        <v>123988447</v>
       </c>
       <c r="B21" t="n">
-        <v>91008</v>
+        <v>57883</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3068,38 +2995,57 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>460222</v>
+        <v>460385</v>
       </c>
       <c r="R21" t="n">
-        <v>7086704</v>
+        <v>7086719</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -3129,11 +3075,21 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3142,23 +3098,28 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123990384</v>
+        <v>123991224</v>
       </c>
       <c r="B22" t="n">
         <v>57883</v>
@@ -3213,14 +3174,14 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>460150</v>
+        <v>460332</v>
       </c>
       <c r="R22" t="n">
-        <v>7086698</v>
+        <v>7086777</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3252,7 +3213,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3262,7 +3223,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3294,10 +3255,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123988998</v>
+        <v>123990384</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3306,41 +3267,60 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>460216</v>
+        <v>460150</v>
       </c>
       <c r="R23" t="n">
-        <v>7086687</v>
+        <v>7086698</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3369,7 +3349,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3379,7 +3359,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3394,26 +3374,6 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3431,10 +3391,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123988915</v>
+        <v>123991476</v>
       </c>
       <c r="B24" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3447,37 +3407,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>460262</v>
+        <v>460544</v>
       </c>
       <c r="R24" t="n">
-        <v>7086681</v>
+        <v>7086749</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3504,11 +3464,26 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3517,23 +3492,48 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123989913</v>
+        <v>123989420</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3573,10 +3573,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>460291</v>
+        <v>460223</v>
       </c>
       <c r="R25" t="n">
-        <v>7086773</v>
+        <v>7086707</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3635,10 +3635,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124025475</v>
+        <v>124025470</v>
       </c>
       <c r="B26" t="n">
-        <v>91030</v>
+        <v>91705</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3647,25 +3647,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>67</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3675,10 +3675,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>460284</v>
+        <v>460140</v>
       </c>
       <c r="R26" t="n">
-        <v>7086722</v>
+        <v>7086711</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3737,10 +3737,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124025470</v>
+        <v>124025467</v>
       </c>
       <c r="B27" t="n">
-        <v>91705</v>
+        <v>57513</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3749,25 +3749,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3777,10 +3777,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>460140</v>
+        <v>460343</v>
       </c>
       <c r="R27" t="n">
-        <v>7086711</v>
+        <v>7086730</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3813,6 +3813,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3946,7 +3951,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124025469</v>
+        <v>124025464</v>
       </c>
       <c r="B29" t="n">
         <v>57513</v>
@@ -3986,10 +3991,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>460378</v>
+        <v>460209</v>
       </c>
       <c r="R29" t="n">
-        <v>7086700</v>
+        <v>7086674</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4026,7 +4031,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack Färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4053,7 +4058,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124025465</v>
+        <v>124025453</v>
       </c>
       <c r="B30" t="n">
         <v>57513</v>
@@ -4093,10 +4098,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>460240</v>
+        <v>460668</v>
       </c>
       <c r="R30" t="n">
-        <v>7086700</v>
+        <v>7086736</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4160,7 +4165,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124025462</v>
+        <v>124025461</v>
       </c>
       <c r="B31" t="n">
         <v>57513</v>
@@ -4200,10 +4205,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>460183</v>
+        <v>460078</v>
       </c>
       <c r="R31" t="n">
-        <v>7086654</v>
+        <v>7086651</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4240,7 +4245,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4267,7 +4272,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124025460</v>
+        <v>124025457</v>
       </c>
       <c r="B32" t="n">
         <v>57513</v>
@@ -4307,10 +4312,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>460124</v>
+        <v>460222</v>
       </c>
       <c r="R32" t="n">
-        <v>7086694</v>
+        <v>7086760</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4347,7 +4352,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4374,10 +4379,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124025476</v>
+        <v>124025462</v>
       </c>
       <c r="B33" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4390,21 +4395,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4414,10 +4419,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>460154</v>
+        <v>460183</v>
       </c>
       <c r="R33" t="n">
-        <v>7086694</v>
+        <v>7086654</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4452,13 +4457,17 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4477,10 +4486,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124025453</v>
+        <v>124025475</v>
       </c>
       <c r="B34" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4493,21 +4502,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4517,10 +4526,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>460668</v>
+        <v>460284</v>
       </c>
       <c r="R34" t="n">
-        <v>7086736</v>
+        <v>7086722</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4553,11 +4562,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4584,10 +4588,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124025467</v>
+        <v>124025476</v>
       </c>
       <c r="B35" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4600,21 +4604,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4624,10 +4628,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>460343</v>
+        <v>460154</v>
       </c>
       <c r="R35" t="n">
-        <v>7086730</v>
+        <v>7086694</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4662,17 +4666,13 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4905,7 +4905,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124025464</v>
+        <v>124025465</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -4945,10 +4945,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>460209</v>
+        <v>460240</v>
       </c>
       <c r="R38" t="n">
-        <v>7086674</v>
+        <v>7086700</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5114,7 +5114,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124025461</v>
+        <v>124025469</v>
       </c>
       <c r="B40" t="n">
         <v>57513</v>
@@ -5154,10 +5154,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>460078</v>
+        <v>460378</v>
       </c>
       <c r="R40" t="n">
-        <v>7086651</v>
+        <v>7086700</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack Färska och äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5221,7 +5221,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124025457</v>
+        <v>124025460</v>
       </c>
       <c r="B41" t="n">
         <v>57513</v>
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>460222</v>
+        <v>460124</v>
       </c>
       <c r="R41" t="n">
-        <v>7086760</v>
+        <v>7086694</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5301,7 +5301,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 60117-2024 artfynd.xlsx
+++ b/artfynd/A 60117-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123988501</v>
+        <v>123988472</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460349</v>
+        <v>460371</v>
       </c>
       <c r="R2" t="n">
-        <v>7086748</v>
+        <v>7086703</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,21 +748,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,51 +761,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123988446</v>
+        <v>123990841</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460371</v>
+        <v>460642</v>
       </c>
       <c r="R3" t="n">
-        <v>7086703</v>
+        <v>7086699</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -914,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123990841</v>
+        <v>123991224</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>57883</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,38 +891,57 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460642</v>
+        <v>460332</v>
       </c>
       <c r="R4" t="n">
-        <v>7086699</v>
+        <v>7086777</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,11 +971,21 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1000,26 +994,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123989913</v>
+        <v>123990830</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,37 +1031,47 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460291</v>
+        <v>460249</v>
       </c>
       <c r="R5" t="n">
-        <v>7086773</v>
+        <v>7086743</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,11 +1098,26 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på en gran.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1102,26 +1126,51 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123989562</v>
+        <v>123989081</v>
       </c>
       <c r="B6" t="n">
-        <v>56714</v>
+        <v>91008</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,42 +1183,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460190</v>
+        <v>460222</v>
       </c>
       <c r="R6" t="n">
-        <v>7086684</v>
+        <v>7086704</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,26 +1240,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:46</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snötäcket i flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1224,31 +1253,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123988808</v>
+        <v>123988998</v>
       </c>
       <c r="B7" t="n">
-        <v>95335</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,41 +1281,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460285</v>
+        <v>460216</v>
       </c>
       <c r="R7" t="n">
-        <v>7086685</v>
+        <v>7086687</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1318,11 +1342,21 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1331,23 +1365,48 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123991344</v>
+        <v>123989420</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1383,17 +1442,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460415</v>
+        <v>460223</v>
       </c>
       <c r="R8" t="n">
-        <v>7086783</v>
+        <v>7086707</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1420,21 +1479,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:36</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:36</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1443,51 +1492,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123989782</v>
+        <v>123990224</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,42 +1524,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460153</v>
+        <v>460370</v>
       </c>
       <c r="R9" t="n">
-        <v>7086693</v>
+        <v>7086712</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1562,26 +1581,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:52</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en stående och en liggande död granstam.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1590,51 +1594,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123990830</v>
+        <v>123987918</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1647,47 +1626,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460249</v>
+        <v>460582</v>
       </c>
       <c r="R10" t="n">
-        <v>7086743</v>
+        <v>7086692</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1716,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1726,12 +1695,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på en gran.</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1760,12 +1724,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1783,10 +1747,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123990224</v>
+        <v>123990384</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1795,41 +1759,60 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460370</v>
+        <v>460150</v>
       </c>
       <c r="R11" t="n">
-        <v>7086712</v>
+        <v>7086698</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1856,11 +1839,21 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1869,26 +1862,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123987913</v>
+        <v>123989562</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>56714</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1901,37 +1899,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>460590</v>
+        <v>460190</v>
       </c>
       <c r="R12" t="n">
-        <v>7086691</v>
+        <v>7086684</v>
       </c>
       <c r="S12" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1958,11 +1961,26 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket i flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1971,26 +1989,31 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123989081</v>
+        <v>123989913</v>
       </c>
       <c r="B13" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2003,21 +2026,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2027,10 +2050,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460222</v>
+        <v>460291</v>
       </c>
       <c r="R13" t="n">
-        <v>7086704</v>
+        <v>7086773</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2089,10 +2112,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123988915</v>
+        <v>123991476</v>
       </c>
       <c r="B14" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2105,37 +2128,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460262</v>
+        <v>460544</v>
       </c>
       <c r="R14" t="n">
-        <v>7086681</v>
+        <v>7086749</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2162,11 +2185,26 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2175,26 +2213,51 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123988998</v>
+        <v>123988447</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2203,41 +2266,60 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460216</v>
+        <v>460385</v>
       </c>
       <c r="R15" t="n">
-        <v>7086687</v>
+        <v>7086719</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2266,7 +2348,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2276,7 +2358,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,26 +2373,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2328,10 +2390,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123990278</v>
+        <v>123988808</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>95335</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2340,41 +2402,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460105</v>
+        <v>460285</v>
       </c>
       <c r="R16" t="n">
-        <v>7086675</v>
+        <v>7086685</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2401,21 +2463,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2424,51 +2476,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123988472</v>
+        <v>123990278</v>
       </c>
       <c r="B17" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2481,37 +2508,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>460371</v>
+        <v>460105</v>
       </c>
       <c r="R17" t="n">
-        <v>7086703</v>
+        <v>7086675</v>
       </c>
       <c r="S17" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2538,11 +2565,21 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2551,23 +2588,48 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123987918</v>
+        <v>123988446</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2607,13 +2669,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>460582</v>
+        <v>460371</v>
       </c>
       <c r="R18" t="n">
-        <v>7086692</v>
+        <v>7086703</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2640,21 +2702,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>09:02</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>09:02</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2663,41 +2715,16 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2983,10 +3010,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123988447</v>
+        <v>123989782</v>
       </c>
       <c r="B21" t="n">
-        <v>57883</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2995,20 +3022,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3016,39 +3043,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>460385</v>
+        <v>460153</v>
       </c>
       <c r="R21" t="n">
-        <v>7086719</v>
+        <v>7086693</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3077,7 +3090,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3087,7 +3100,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en stående och en liggande död granstam.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3102,6 +3120,26 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3119,10 +3157,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123991224</v>
+        <v>123988915</v>
       </c>
       <c r="B22" t="n">
-        <v>57883</v>
+        <v>91008</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3131,60 +3169,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>460332</v>
+        <v>460262</v>
       </c>
       <c r="R22" t="n">
-        <v>7086777</v>
+        <v>7086681</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3211,21 +3230,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3234,31 +3243,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123990384</v>
+        <v>123988501</v>
       </c>
       <c r="B23" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3267,60 +3271,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>460150</v>
+        <v>460349</v>
       </c>
       <c r="R23" t="n">
-        <v>7086698</v>
+        <v>7086748</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3349,7 +3334,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3359,7 +3344,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3374,6 +3359,26 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3391,10 +3396,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123991476</v>
+        <v>123987913</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3407,21 +3412,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3431,13 +3436,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>460544</v>
+        <v>460590</v>
       </c>
       <c r="R24" t="n">
-        <v>7086749</v>
+        <v>7086691</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3464,26 +3469,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3492,48 +3482,23 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123989420</v>
+        <v>123991344</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3569,17 +3534,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>460223</v>
+        <v>460415</v>
       </c>
       <c r="R25" t="n">
-        <v>7086707</v>
+        <v>7086783</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3606,11 +3571,21 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3619,26 +3594,51 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124025470</v>
+        <v>124025467</v>
       </c>
       <c r="B26" t="n">
-        <v>91705</v>
+        <v>57513</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3647,25 +3647,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3675,10 +3675,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>460140</v>
+        <v>460343</v>
       </c>
       <c r="R26" t="n">
-        <v>7086711</v>
+        <v>7086730</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3711,6 +3711,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3737,7 +3742,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124025467</v>
+        <v>124025453</v>
       </c>
       <c r="B27" t="n">
         <v>57513</v>
@@ -3777,10 +3782,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>460343</v>
+        <v>460668</v>
       </c>
       <c r="R27" t="n">
-        <v>7086730</v>
+        <v>7086736</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3844,10 +3849,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124025458</v>
+        <v>124025470</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>91705</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3856,25 +3861,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3884,10 +3889,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>460205</v>
+        <v>460140</v>
       </c>
       <c r="R28" t="n">
-        <v>7086746</v>
+        <v>7086711</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3920,11 +3925,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3951,7 +3951,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124025464</v>
+        <v>124025457</v>
       </c>
       <c r="B29" t="n">
         <v>57513</v>
@@ -3991,10 +3991,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>460209</v>
+        <v>460222</v>
       </c>
       <c r="R29" t="n">
-        <v>7086674</v>
+        <v>7086760</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4058,10 +4058,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124025453</v>
+        <v>124025476</v>
       </c>
       <c r="B30" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4074,21 +4074,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4098,10 +4098,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>460668</v>
+        <v>460154</v>
       </c>
       <c r="R30" t="n">
-        <v>7086736</v>
+        <v>7086694</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4136,17 +4136,13 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4165,7 +4161,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124025461</v>
+        <v>124025462</v>
       </c>
       <c r="B31" t="n">
         <v>57513</v>
@@ -4205,10 +4201,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>460078</v>
+        <v>460183</v>
       </c>
       <c r="R31" t="n">
-        <v>7086651</v>
+        <v>7086654</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4245,7 +4241,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4272,7 +4268,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124025457</v>
+        <v>124025459</v>
       </c>
       <c r="B32" t="n">
         <v>57513</v>
@@ -4312,10 +4308,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>460222</v>
+        <v>460150</v>
       </c>
       <c r="R32" t="n">
-        <v>7086760</v>
+        <v>7086691</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4352,7 +4348,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4379,7 +4375,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124025462</v>
+        <v>124025456</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -4419,10 +4415,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>460183</v>
+        <v>460284</v>
       </c>
       <c r="R33" t="n">
-        <v>7086654</v>
+        <v>7086765</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4486,7 +4482,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124025475</v>
+        <v>124025473</v>
       </c>
       <c r="B34" t="n">
         <v>91030</v>
@@ -4526,10 +4522,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>460284</v>
+        <v>460235</v>
       </c>
       <c r="R34" t="n">
-        <v>7086722</v>
+        <v>7086681</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4588,10 +4584,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124025476</v>
+        <v>124025465</v>
       </c>
       <c r="B35" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4604,21 +4600,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4628,10 +4624,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>460154</v>
+        <v>460240</v>
       </c>
       <c r="R35" t="n">
-        <v>7086694</v>
+        <v>7086700</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4666,13 +4662,17 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4691,7 +4691,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124025459</v>
+        <v>124025460</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>460150</v>
+        <v>460124</v>
       </c>
       <c r="R36" t="n">
-        <v>7086691</v>
+        <v>7086694</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4798,7 +4798,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124025456</v>
+        <v>124025464</v>
       </c>
       <c r="B37" t="n">
         <v>57513</v>
@@ -4838,10 +4838,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>460284</v>
+        <v>460209</v>
       </c>
       <c r="R37" t="n">
-        <v>7086765</v>
+        <v>7086674</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4905,7 +4905,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124025465</v>
+        <v>124025461</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -4945,10 +4945,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>460240</v>
+        <v>460078</v>
       </c>
       <c r="R38" t="n">
-        <v>7086700</v>
+        <v>7086651</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4985,7 +4985,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5012,10 +5012,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124025473</v>
+        <v>124025469</v>
       </c>
       <c r="B39" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5028,21 +5028,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5052,10 +5052,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>460235</v>
+        <v>460378</v>
       </c>
       <c r="R39" t="n">
-        <v>7086681</v>
+        <v>7086700</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5088,6 +5088,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack Färska och äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5114,7 +5119,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124025469</v>
+        <v>124025458</v>
       </c>
       <c r="B40" t="n">
         <v>57513</v>
@@ -5154,10 +5159,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>460378</v>
+        <v>460205</v>
       </c>
       <c r="R40" t="n">
-        <v>7086700</v>
+        <v>7086746</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5194,7 +5199,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack Färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5221,10 +5226,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124025460</v>
+        <v>124025475</v>
       </c>
       <c r="B41" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5237,21 +5242,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5261,10 +5266,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>460124</v>
+        <v>460284</v>
       </c>
       <c r="R41" t="n">
-        <v>7086694</v>
+        <v>7086722</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5297,11 +5302,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 60117-2024 artfynd.xlsx
+++ b/artfynd/A 60117-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123988472</v>
+        <v>123990849</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460371</v>
+        <v>460241</v>
       </c>
       <c r="R2" t="n">
-        <v>7086703</v>
+        <v>7086734</v>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,11 +748,21 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -761,26 +771,51 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123990841</v>
+        <v>123990830</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +828,47 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460642</v>
+        <v>460249</v>
       </c>
       <c r="R3" t="n">
-        <v>7086699</v>
+        <v>7086743</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,11 +895,26 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på en gran.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -863,26 +923,51 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123991224</v>
+        <v>123988998</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,60 +976,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460332</v>
+        <v>460216</v>
       </c>
       <c r="R4" t="n">
-        <v>7086777</v>
+        <v>7086687</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,7 +1039,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,7 +1049,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,6 +1064,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1015,10 +1101,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123990830</v>
+        <v>123987918</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,47 +1117,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460249</v>
+        <v>460582</v>
       </c>
       <c r="R5" t="n">
-        <v>7086743</v>
+        <v>7086692</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,7 +1176,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,12 +1186,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på en gran.</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,12 +1215,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1167,10 +1238,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123989081</v>
+        <v>123989420</v>
       </c>
       <c r="B6" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1183,21 +1254,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1207,10 +1278,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460222</v>
+        <v>460223</v>
       </c>
       <c r="R6" t="n">
-        <v>7086704</v>
+        <v>7086707</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1269,10 +1340,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123988998</v>
+        <v>123989562</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,37 +1356,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460216</v>
+        <v>460190</v>
       </c>
       <c r="R7" t="n">
-        <v>7086687</v>
+        <v>7086684</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1344,7 +1420,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,7 +1430,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket i flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,26 +1450,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1406,7 +1467,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123989420</v>
+        <v>123991344</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1442,17 +1503,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460223</v>
+        <v>460415</v>
       </c>
       <c r="R8" t="n">
-        <v>7086707</v>
+        <v>7086783</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1479,11 +1540,21 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1492,26 +1563,51 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123990224</v>
+        <v>123988915</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1524,34 +1620,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460370</v>
+        <v>460262</v>
       </c>
       <c r="R9" t="n">
-        <v>7086712</v>
+        <v>7086681</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1610,10 +1706,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123987918</v>
+        <v>123989081</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1626,37 +1722,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460582</v>
+        <v>460222</v>
       </c>
       <c r="R10" t="n">
-        <v>7086692</v>
+        <v>7086704</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1683,21 +1779,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:02</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:02</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1706,51 +1792,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123990384</v>
+        <v>123990841</v>
       </c>
       <c r="B11" t="n">
-        <v>57883</v>
+        <v>57666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1759,57 +1820,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460150</v>
+        <v>460642</v>
       </c>
       <c r="R11" t="n">
-        <v>7086698</v>
+        <v>7086699</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1839,21 +1881,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10:08</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>10:08</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1862,31 +1894,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123989562</v>
+        <v>123989913</v>
       </c>
       <c r="B12" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1899,42 +1926,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>460190</v>
+        <v>460291</v>
       </c>
       <c r="R12" t="n">
-        <v>7086684</v>
+        <v>7086773</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1961,26 +1983,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>09:46</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snötäcket i flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1989,28 +1996,23 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123989913</v>
+        <v>123988446</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -2046,14 +2048,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460291</v>
+        <v>460371</v>
       </c>
       <c r="R13" t="n">
-        <v>7086773</v>
+        <v>7086703</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2112,7 +2114,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123991476</v>
+        <v>123990278</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -2148,14 +2150,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460544</v>
+        <v>460105</v>
       </c>
       <c r="R14" t="n">
-        <v>7086749</v>
+        <v>7086675</v>
       </c>
       <c r="S14" t="n">
         <v>8</v>
@@ -2187,7 +2189,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2197,12 +2199,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2254,7 +2251,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123988447</v>
+        <v>123991224</v>
       </c>
       <c r="B15" t="n">
         <v>57883</v>
@@ -2313,13 +2310,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460385</v>
+        <v>460332</v>
       </c>
       <c r="R15" t="n">
-        <v>7086719</v>
+        <v>7086777</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2348,7 +2345,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2358,7 +2355,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2390,10 +2387,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123988808</v>
+        <v>123990384</v>
       </c>
       <c r="B16" t="n">
-        <v>95335</v>
+        <v>57883</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2406,37 +2403,56 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2809</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460285</v>
+        <v>460150</v>
       </c>
       <c r="R16" t="n">
-        <v>7086685</v>
+        <v>7086698</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2463,11 +2479,21 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2476,26 +2502,31 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123990278</v>
+        <v>123987913</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2508,37 +2539,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>460105</v>
+        <v>460590</v>
       </c>
       <c r="R17" t="n">
-        <v>7086675</v>
+        <v>7086691</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2565,21 +2596,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2588,48 +2609,23 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123988446</v>
+        <v>123988501</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2669,13 +2665,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>460371</v>
+        <v>460349</v>
       </c>
       <c r="R18" t="n">
-        <v>7086703</v>
+        <v>7086748</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2702,11 +2698,21 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2715,26 +2721,51 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123991060</v>
+        <v>123988447</v>
       </c>
       <c r="B19" t="n">
-        <v>91030</v>
+        <v>57883</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2743,46 +2774,60 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>460261</v>
+        <v>460385</v>
       </c>
       <c r="R19" t="n">
-        <v>7086790</v>
+        <v>7086719</v>
       </c>
       <c r="S19" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2811,7 +2856,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2821,7 +2866,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2836,26 +2881,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2873,10 +2898,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123990849</v>
+        <v>123988808</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>95335</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2885,41 +2910,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>460241</v>
+        <v>460285</v>
       </c>
       <c r="R20" t="n">
-        <v>7086734</v>
+        <v>7086685</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2946,21 +2971,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2969,51 +2984,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123989782</v>
+        <v>123990224</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3026,42 +3016,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>460153</v>
+        <v>460370</v>
       </c>
       <c r="R21" t="n">
-        <v>7086693</v>
+        <v>7086712</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3088,26 +3073,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>09:52</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en stående och en liggande död granstam.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3116,51 +3086,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123988915</v>
+        <v>123989782</v>
       </c>
       <c r="B22" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3173,37 +3118,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>460262</v>
+        <v>460153</v>
       </c>
       <c r="R22" t="n">
-        <v>7086681</v>
+        <v>7086693</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3230,11 +3180,26 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en stående och en liggande död granstam.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3243,26 +3208,51 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123988501</v>
+        <v>123991060</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3275,37 +3265,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>460349</v>
+        <v>460261</v>
       </c>
       <c r="R23" t="n">
-        <v>7086748</v>
+        <v>7086790</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3334,7 +3329,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3344,7 +3339,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3373,12 +3368,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3396,10 +3391,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123987913</v>
+        <v>123988472</v>
       </c>
       <c r="B24" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3412,21 +3407,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3436,10 +3431,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>460590</v>
+        <v>460371</v>
       </c>
       <c r="R24" t="n">
-        <v>7086691</v>
+        <v>7086703</v>
       </c>
       <c r="S24" t="n">
         <v>30</v>
@@ -3498,7 +3493,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123991344</v>
+        <v>123991476</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3538,13 +3533,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>460415</v>
+        <v>460544</v>
       </c>
       <c r="R25" t="n">
-        <v>7086783</v>
+        <v>7086749</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3573,7 +3568,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3583,7 +3578,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3635,7 +3635,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124025467</v>
+        <v>124025457</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3675,10 +3675,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>460343</v>
+        <v>460222</v>
       </c>
       <c r="R26" t="n">
-        <v>7086730</v>
+        <v>7086760</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3742,7 +3742,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124025453</v>
+        <v>124025460</v>
       </c>
       <c r="B27" t="n">
         <v>57513</v>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>460668</v>
+        <v>460124</v>
       </c>
       <c r="R27" t="n">
-        <v>7086736</v>
+        <v>7086694</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3849,10 +3849,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124025470</v>
+        <v>124025459</v>
       </c>
       <c r="B28" t="n">
-        <v>91705</v>
+        <v>57513</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3861,25 +3861,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3889,10 +3889,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>460140</v>
+        <v>460150</v>
       </c>
       <c r="R28" t="n">
-        <v>7086711</v>
+        <v>7086691</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3925,6 +3925,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3951,10 +3956,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124025457</v>
+        <v>124025476</v>
       </c>
       <c r="B29" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3967,21 +3972,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3991,10 +3996,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>460222</v>
+        <v>460154</v>
       </c>
       <c r="R29" t="n">
-        <v>7086760</v>
+        <v>7086694</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4029,17 +4034,13 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4058,10 +4059,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124025476</v>
+        <v>124025462</v>
       </c>
       <c r="B30" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4074,21 +4075,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4098,10 +4099,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>460154</v>
+        <v>460183</v>
       </c>
       <c r="R30" t="n">
-        <v>7086694</v>
+        <v>7086654</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4136,13 +4137,17 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4161,10 +4166,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124025462</v>
+        <v>124025475</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4177,21 +4182,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4201,10 +4206,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>460183</v>
+        <v>460284</v>
       </c>
       <c r="R31" t="n">
-        <v>7086654</v>
+        <v>7086722</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4237,11 +4242,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4268,7 +4268,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124025459</v>
+        <v>124025469</v>
       </c>
       <c r="B32" t="n">
         <v>57513</v>
@@ -4308,10 +4308,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>460150</v>
+        <v>460378</v>
       </c>
       <c r="R32" t="n">
-        <v>7086691</v>
+        <v>7086700</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4348,7 +4348,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack Färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4375,10 +4375,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124025456</v>
+        <v>124025470</v>
       </c>
       <c r="B33" t="n">
-        <v>57513</v>
+        <v>91705</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4387,25 +4387,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4415,10 +4415,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>460284</v>
+        <v>460140</v>
       </c>
       <c r="R33" t="n">
-        <v>7086765</v>
+        <v>7086711</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4451,11 +4451,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4482,10 +4477,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124025473</v>
+        <v>124025458</v>
       </c>
       <c r="B34" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4498,21 +4493,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4522,10 +4517,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>460235</v>
+        <v>460205</v>
       </c>
       <c r="R34" t="n">
-        <v>7086681</v>
+        <v>7086746</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4558,6 +4553,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4584,7 +4584,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124025465</v>
+        <v>124025464</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -4624,10 +4624,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>460240</v>
+        <v>460209</v>
       </c>
       <c r="R35" t="n">
-        <v>7086700</v>
+        <v>7086674</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4691,7 +4691,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124025460</v>
+        <v>124025467</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>460124</v>
+        <v>460343</v>
       </c>
       <c r="R36" t="n">
-        <v>7086694</v>
+        <v>7086730</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4798,7 +4798,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124025464</v>
+        <v>124025456</v>
       </c>
       <c r="B37" t="n">
         <v>57513</v>
@@ -4838,10 +4838,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>460209</v>
+        <v>460284</v>
       </c>
       <c r="R37" t="n">
-        <v>7086674</v>
+        <v>7086765</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4905,10 +4905,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124025461</v>
+        <v>124025473</v>
       </c>
       <c r="B38" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4921,21 +4921,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4945,10 +4945,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>460078</v>
+        <v>460235</v>
       </c>
       <c r="R38" t="n">
-        <v>7086651</v>
+        <v>7086681</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4981,11 +4981,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5012,7 +5007,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124025469</v>
+        <v>124025453</v>
       </c>
       <c r="B39" t="n">
         <v>57513</v>
@@ -5052,10 +5047,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>460378</v>
+        <v>460668</v>
       </c>
       <c r="R39" t="n">
-        <v>7086700</v>
+        <v>7086736</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5092,7 +5087,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack Färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5119,7 +5114,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124025458</v>
+        <v>124025465</v>
       </c>
       <c r="B40" t="n">
         <v>57513</v>
@@ -5159,10 +5154,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>460205</v>
+        <v>460240</v>
       </c>
       <c r="R40" t="n">
-        <v>7086746</v>
+        <v>7086700</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5226,10 +5221,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124025475</v>
+        <v>124025461</v>
       </c>
       <c r="B41" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5242,21 +5237,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5266,10 +5261,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>460284</v>
+        <v>460078</v>
       </c>
       <c r="R41" t="n">
-        <v>7086722</v>
+        <v>7086651</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5302,6 +5297,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 60117-2024 artfynd.xlsx
+++ b/artfynd/A 60117-2024 artfynd.xlsx
@@ -1467,10 +1467,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123991344</v>
+        <v>123988915</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1483,37 +1483,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460415</v>
+        <v>460262</v>
       </c>
       <c r="R8" t="n">
-        <v>7086783</v>
+        <v>7086681</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1540,21 +1540,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:36</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:36</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1563,51 +1553,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123988915</v>
+        <v>123991344</v>
       </c>
       <c r="B9" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1620,37 +1585,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460262</v>
+        <v>460415</v>
       </c>
       <c r="R9" t="n">
-        <v>7086681</v>
+        <v>7086783</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1677,11 +1642,21 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1690,16 +1665,41 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123988501</v>
+        <v>123988447</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2637,41 +2637,60 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>460349</v>
+        <v>460385</v>
       </c>
       <c r="R18" t="n">
-        <v>7086748</v>
+        <v>7086719</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2700,7 +2719,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2710,7 +2729,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2725,26 +2744,6 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2762,10 +2761,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123988447</v>
+        <v>123988501</v>
       </c>
       <c r="B19" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2774,60 +2773,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>460385</v>
+        <v>460349</v>
       </c>
       <c r="R19" t="n">
-        <v>7086719</v>
+        <v>7086748</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2856,7 +2836,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2866,7 +2846,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2881,6 +2861,26 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3391,10 +3391,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123988472</v>
+        <v>123991476</v>
       </c>
       <c r="B24" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3407,21 +3407,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3431,13 +3431,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>460371</v>
+        <v>460544</v>
       </c>
       <c r="R24" t="n">
-        <v>7086703</v>
+        <v>7086749</v>
       </c>
       <c r="S24" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3464,11 +3464,26 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3477,26 +3492,51 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123991476</v>
+        <v>123988472</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3509,21 +3549,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3533,13 +3573,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>460544</v>
+        <v>460371</v>
       </c>
       <c r="R25" t="n">
-        <v>7086749</v>
+        <v>7086703</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3566,26 +3606,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3594,41 +3619,16 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 60117-2024 artfynd.xlsx
+++ b/artfynd/A 60117-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123990849</v>
+        <v>123990224</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -711,17 +711,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460241</v>
+        <v>460370</v>
       </c>
       <c r="R2" t="n">
-        <v>7086734</v>
+        <v>7086712</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,21 +748,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,51 +761,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123990830</v>
+        <v>123987913</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,47 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460249</v>
+        <v>460590</v>
       </c>
       <c r="R3" t="n">
-        <v>7086743</v>
+        <v>7086691</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,26 +850,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på en gran.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -923,51 +863,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123988998</v>
+        <v>123991060</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -980,37 +895,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460216</v>
+        <v>460261</v>
       </c>
       <c r="R4" t="n">
-        <v>7086687</v>
+        <v>7086790</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1039,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1049,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1078,12 +998,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1101,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123987918</v>
+        <v>123990830</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1117,37 +1037,47 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460582</v>
+        <v>460249</v>
       </c>
       <c r="R5" t="n">
-        <v>7086692</v>
+        <v>7086743</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1176,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1186,7 +1116,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1215,12 +1150,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1238,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123989420</v>
+        <v>123990841</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1254,37 +1189,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460223</v>
+        <v>460642</v>
       </c>
       <c r="R6" t="n">
-        <v>7086707</v>
+        <v>7086699</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1340,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123989562</v>
+        <v>123988447</v>
       </c>
       <c r="B7" t="n">
-        <v>56714</v>
+        <v>57883</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1352,20 +1287,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1373,25 +1308,39 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460190</v>
+        <v>460385</v>
       </c>
       <c r="R7" t="n">
-        <v>7086684</v>
+        <v>7086719</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1420,7 +1369,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1430,12 +1379,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snötäcket i flerskiktad granskog.</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1467,10 +1411,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123988915</v>
+        <v>123988998</v>
       </c>
       <c r="B8" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1483,21 +1427,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1507,13 +1451,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460262</v>
+        <v>460216</v>
       </c>
       <c r="R8" t="n">
-        <v>7086681</v>
+        <v>7086687</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1540,11 +1484,21 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1553,26 +1507,51 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123991344</v>
+        <v>123989562</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1585,37 +1564,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460415</v>
+        <v>460190</v>
       </c>
       <c r="R9" t="n">
-        <v>7086783</v>
+        <v>7086684</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1644,7 +1628,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1654,7 +1638,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket i flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1669,26 +1658,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1706,10 +1675,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123989081</v>
+        <v>123988808</v>
       </c>
       <c r="B10" t="n">
-        <v>91008</v>
+        <v>95335</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1718,38 +1687,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>2809</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460222</v>
+        <v>460285</v>
       </c>
       <c r="R10" t="n">
-        <v>7086704</v>
+        <v>7086685</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1808,10 +1777,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123990841</v>
+        <v>123991344</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1824,37 +1793,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460642</v>
+        <v>460415</v>
       </c>
       <c r="R11" t="n">
-        <v>7086699</v>
+        <v>7086783</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1881,11 +1850,21 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1894,23 +1873,48 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123989913</v>
+        <v>123987918</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1946,17 +1950,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>460291</v>
+        <v>460582</v>
       </c>
       <c r="R12" t="n">
-        <v>7086773</v>
+        <v>7086692</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1983,11 +1987,21 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1996,23 +2010,48 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123988446</v>
+        <v>123989913</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -2048,14 +2087,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460371</v>
+        <v>460291</v>
       </c>
       <c r="R13" t="n">
-        <v>7086703</v>
+        <v>7086773</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2114,10 +2153,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123990278</v>
+        <v>123989782</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2130,37 +2169,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460105</v>
+        <v>460153</v>
       </c>
       <c r="R14" t="n">
-        <v>7086675</v>
+        <v>7086693</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2189,7 +2233,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2199,7 +2243,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en stående och en liggande död granstam.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2228,12 +2277,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2251,10 +2300,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123991224</v>
+        <v>123990278</v>
       </c>
       <c r="B15" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2263,60 +2312,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460332</v>
+        <v>460105</v>
       </c>
       <c r="R15" t="n">
-        <v>7086777</v>
+        <v>7086675</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2345,7 +2375,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2355,7 +2385,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2370,6 +2400,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2387,10 +2437,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123990384</v>
+        <v>123991476</v>
       </c>
       <c r="B16" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2399,60 +2449,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460150</v>
+        <v>460544</v>
       </c>
       <c r="R16" t="n">
-        <v>7086698</v>
+        <v>7086749</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2481,7 +2512,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2491,7 +2522,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2506,6 +2542,26 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2523,10 +2579,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123987913</v>
+        <v>123991224</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>57883</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2535,41 +2591,60 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>460590</v>
+        <v>460332</v>
       </c>
       <c r="R17" t="n">
-        <v>7086691</v>
+        <v>7086777</v>
       </c>
       <c r="S17" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2596,11 +2671,21 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2609,23 +2694,28 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123988447</v>
+        <v>123990384</v>
       </c>
       <c r="B18" t="n">
         <v>57883</v>
@@ -2680,17 +2770,17 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>460385</v>
+        <v>460150</v>
       </c>
       <c r="R18" t="n">
-        <v>7086719</v>
+        <v>7086698</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2719,7 +2809,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2729,7 +2819,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2761,7 +2851,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123988501</v>
+        <v>123990849</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2797,17 +2887,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>460349</v>
+        <v>460241</v>
       </c>
       <c r="R19" t="n">
-        <v>7086748</v>
+        <v>7086734</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2836,7 +2926,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2846,7 +2936,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2898,10 +2988,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123988808</v>
+        <v>123989081</v>
       </c>
       <c r="B20" t="n">
-        <v>95335</v>
+        <v>91008</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2910,38 +3000,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2809</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>460285</v>
+        <v>460222</v>
       </c>
       <c r="R20" t="n">
-        <v>7086685</v>
+        <v>7086704</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -3000,10 +3090,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123990224</v>
+        <v>123988915</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3016,34 +3106,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>460370</v>
+        <v>460262</v>
       </c>
       <c r="R21" t="n">
-        <v>7086712</v>
+        <v>7086681</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -3102,10 +3192,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123989782</v>
+        <v>123988446</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3118,42 +3208,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>460153</v>
+        <v>460371</v>
       </c>
       <c r="R22" t="n">
-        <v>7086693</v>
+        <v>7086703</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3180,26 +3265,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>09:52</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en stående och en liggande död granstam.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3208,51 +3278,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123991060</v>
+        <v>123989420</v>
       </c>
       <c r="B23" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3265,42 +3310,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>460261</v>
+        <v>460223</v>
       </c>
       <c r="R23" t="n">
-        <v>7086790</v>
+        <v>7086707</v>
       </c>
       <c r="S23" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3327,21 +3367,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3350,48 +3380,23 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123991476</v>
+        <v>123988501</v>
       </c>
       <c r="B24" t="n">
         <v>78810</v>
@@ -3431,13 +3436,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>460544</v>
+        <v>460349</v>
       </c>
       <c r="R24" t="n">
-        <v>7086749</v>
+        <v>7086748</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3466,7 +3471,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3476,12 +3481,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3635,7 +3635,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124025457</v>
+        <v>124025469</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3675,10 +3675,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>460222</v>
+        <v>460378</v>
       </c>
       <c r="R26" t="n">
-        <v>7086760</v>
+        <v>7086700</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack Färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3742,7 +3742,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124025460</v>
+        <v>124025459</v>
       </c>
       <c r="B27" t="n">
         <v>57513</v>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>460124</v>
+        <v>460150</v>
       </c>
       <c r="R27" t="n">
-        <v>7086694</v>
+        <v>7086691</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3849,7 +3849,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124025459</v>
+        <v>124025456</v>
       </c>
       <c r="B28" t="n">
         <v>57513</v>
@@ -3889,10 +3889,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>460150</v>
+        <v>460284</v>
       </c>
       <c r="R28" t="n">
-        <v>7086691</v>
+        <v>7086765</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4059,10 +4059,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124025462</v>
+        <v>124025475</v>
       </c>
       <c r="B30" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4075,21 +4075,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4099,10 +4099,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>460183</v>
+        <v>460284</v>
       </c>
       <c r="R30" t="n">
-        <v>7086654</v>
+        <v>7086722</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4135,11 +4135,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4166,10 +4161,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124025475</v>
+        <v>124025467</v>
       </c>
       <c r="B31" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4182,21 +4177,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4206,10 +4201,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>460284</v>
+        <v>460343</v>
       </c>
       <c r="R31" t="n">
-        <v>7086722</v>
+        <v>7086730</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4242,6 +4237,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4268,10 +4268,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124025469</v>
+        <v>124025473</v>
       </c>
       <c r="B32" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4284,21 +4284,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4308,10 +4308,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>460378</v>
+        <v>460235</v>
       </c>
       <c r="R32" t="n">
-        <v>7086700</v>
+        <v>7086681</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4344,11 +4344,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack Färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4375,10 +4370,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124025470</v>
+        <v>124025453</v>
       </c>
       <c r="B33" t="n">
-        <v>91705</v>
+        <v>57513</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4387,25 +4382,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4415,10 +4410,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>460140</v>
+        <v>460668</v>
       </c>
       <c r="R33" t="n">
-        <v>7086711</v>
+        <v>7086736</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4451,6 +4446,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4477,7 +4477,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124025458</v>
+        <v>124025462</v>
       </c>
       <c r="B34" t="n">
         <v>57513</v>
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>460205</v>
+        <v>460183</v>
       </c>
       <c r="R34" t="n">
-        <v>7086746</v>
+        <v>7086654</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4584,7 +4584,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124025464</v>
+        <v>124025461</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -4624,10 +4624,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>460209</v>
+        <v>460078</v>
       </c>
       <c r="R35" t="n">
-        <v>7086674</v>
+        <v>7086651</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4664,7 +4664,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4691,7 +4691,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124025467</v>
+        <v>124025465</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>460343</v>
+        <v>460240</v>
       </c>
       <c r="R36" t="n">
-        <v>7086730</v>
+        <v>7086700</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4798,7 +4798,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124025456</v>
+        <v>124025457</v>
       </c>
       <c r="B37" t="n">
         <v>57513</v>
@@ -4838,10 +4838,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>460284</v>
+        <v>460222</v>
       </c>
       <c r="R37" t="n">
-        <v>7086765</v>
+        <v>7086760</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4905,10 +4905,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124025473</v>
+        <v>124025458</v>
       </c>
       <c r="B38" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4921,21 +4921,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4945,10 +4945,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>460235</v>
+        <v>460205</v>
       </c>
       <c r="R38" t="n">
-        <v>7086681</v>
+        <v>7086746</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4981,6 +4981,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5007,10 +5012,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124025453</v>
+        <v>124025470</v>
       </c>
       <c r="B39" t="n">
-        <v>57513</v>
+        <v>91705</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5019,25 +5024,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5047,10 +5052,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>460668</v>
+        <v>460140</v>
       </c>
       <c r="R39" t="n">
-        <v>7086736</v>
+        <v>7086711</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5083,11 +5088,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5114,7 +5114,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124025465</v>
+        <v>124025460</v>
       </c>
       <c r="B40" t="n">
         <v>57513</v>
@@ -5154,10 +5154,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>460240</v>
+        <v>460124</v>
       </c>
       <c r="R40" t="n">
-        <v>7086700</v>
+        <v>7086694</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5221,7 +5221,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124025461</v>
+        <v>124025464</v>
       </c>
       <c r="B41" t="n">
         <v>57513</v>
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>460078</v>
+        <v>460209</v>
       </c>
       <c r="R41" t="n">
-        <v>7086651</v>
+        <v>7086674</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5301,7 +5301,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 60117-2024 artfynd.xlsx
+++ b/artfynd/A 60117-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123990224</v>
+        <v>123987913</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460370</v>
+        <v>460590</v>
       </c>
       <c r="R2" t="n">
-        <v>7086712</v>
+        <v>7086691</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123987913</v>
+        <v>123990830</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +793,47 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460590</v>
+        <v>460249</v>
       </c>
       <c r="R3" t="n">
-        <v>7086691</v>
+        <v>7086743</v>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,11 +860,26 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på en gran.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -863,26 +888,51 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123991060</v>
+        <v>123990224</v>
       </c>
       <c r="B4" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,42 +945,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460261</v>
+        <v>460370</v>
       </c>
       <c r="R4" t="n">
-        <v>7086790</v>
+        <v>7086712</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,21 +1002,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -980,51 +1015,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123990830</v>
+        <v>123991060</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,32 +1047,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1071,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460249</v>
+        <v>460261</v>
       </c>
       <c r="R5" t="n">
-        <v>7086743</v>
+        <v>7086790</v>
       </c>
       <c r="S5" t="n">
         <v>11</v>
@@ -1106,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,12 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på en gran.</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1411,10 +1411,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123988998</v>
+        <v>123989562</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1427,37 +1427,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460216</v>
+        <v>460190</v>
       </c>
       <c r="R8" t="n">
-        <v>7086687</v>
+        <v>7086684</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1486,7 +1491,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1496,7 +1501,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färsk spillning ovanpå snötäcket i flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,26 +1521,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1548,10 +1538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123989562</v>
+        <v>123988998</v>
       </c>
       <c r="B9" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1564,42 +1554,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460190</v>
+        <v>460216</v>
       </c>
       <c r="R9" t="n">
-        <v>7086684</v>
+        <v>7086687</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1628,7 +1613,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1638,12 +1623,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snötäcket i flerskiktad granskog.</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1658,6 +1638,26 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123989782</v>
+        <v>123990278</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2169,42 +2169,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460153</v>
+        <v>460105</v>
       </c>
       <c r="R14" t="n">
-        <v>7086693</v>
+        <v>7086675</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2233,7 +2228,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2243,12 +2238,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en stående och en liggande död granstam.</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2277,12 +2267,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2300,10 +2290,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123990278</v>
+        <v>123989782</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2316,37 +2306,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460105</v>
+        <v>460153</v>
       </c>
       <c r="R15" t="n">
-        <v>7086675</v>
+        <v>7086693</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2375,7 +2370,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2385,7 +2380,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en stående och en liggande död granstam.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2414,12 +2414,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -3090,10 +3090,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123988915</v>
+        <v>123988446</v>
       </c>
       <c r="B21" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3106,34 +3106,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>460262</v>
+        <v>460371</v>
       </c>
       <c r="R21" t="n">
-        <v>7086681</v>
+        <v>7086703</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -3192,7 +3192,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123988446</v>
+        <v>123989420</v>
       </c>
       <c r="B22" t="n">
         <v>78810</v>
@@ -3228,14 +3228,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>460371</v>
+        <v>460223</v>
       </c>
       <c r="R22" t="n">
-        <v>7086703</v>
+        <v>7086707</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3294,10 +3294,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123989420</v>
+        <v>123988915</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3310,21 +3310,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>460223</v>
+        <v>460262</v>
       </c>
       <c r="R23" t="n">
-        <v>7086707</v>
+        <v>7086681</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -5012,10 +5012,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124025470</v>
+        <v>124025460</v>
       </c>
       <c r="B39" t="n">
-        <v>91705</v>
+        <v>57513</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5024,25 +5024,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5052,10 +5052,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>460140</v>
+        <v>460124</v>
       </c>
       <c r="R39" t="n">
-        <v>7086711</v>
+        <v>7086694</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5088,6 +5088,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5114,7 +5119,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124025460</v>
+        <v>124025464</v>
       </c>
       <c r="B40" t="n">
         <v>57513</v>
@@ -5154,10 +5159,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>460124</v>
+        <v>460209</v>
       </c>
       <c r="R40" t="n">
-        <v>7086694</v>
+        <v>7086674</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5221,10 +5226,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124025464</v>
+        <v>124025470</v>
       </c>
       <c r="B41" t="n">
-        <v>57513</v>
+        <v>91705</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5233,25 +5238,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5261,10 +5266,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>460209</v>
+        <v>460140</v>
       </c>
       <c r="R41" t="n">
-        <v>7086674</v>
+        <v>7086711</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5297,11 +5302,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 60117-2024 artfynd.xlsx
+++ b/artfynd/A 60117-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123987913</v>
+        <v>123990224</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460590</v>
+        <v>460370</v>
       </c>
       <c r="R2" t="n">
-        <v>7086691</v>
+        <v>7086712</v>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123990830</v>
+        <v>123987913</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,47 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460249</v>
+        <v>460590</v>
       </c>
       <c r="R3" t="n">
-        <v>7086743</v>
+        <v>7086691</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,26 +850,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på en gran.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -888,51 +863,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123990224</v>
+        <v>123991060</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,37 +895,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460370</v>
+        <v>460261</v>
       </c>
       <c r="R4" t="n">
-        <v>7086712</v>
+        <v>7086790</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,11 +957,21 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1015,26 +980,51 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123991060</v>
+        <v>123990830</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,27 +1037,32 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1076,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460261</v>
+        <v>460249</v>
       </c>
       <c r="R5" t="n">
-        <v>7086790</v>
+        <v>7086743</v>
       </c>
       <c r="S5" t="n">
         <v>11</v>
@@ -1111,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1116,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på en gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1675,10 +1675,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123988808</v>
+        <v>123991344</v>
       </c>
       <c r="B10" t="n">
-        <v>95335</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1687,25 +1687,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460285</v>
+        <v>460415</v>
       </c>
       <c r="R10" t="n">
-        <v>7086685</v>
+        <v>7086783</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1748,11 +1748,21 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1761,23 +1771,48 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123991344</v>
+        <v>123987918</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1817,13 +1852,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460415</v>
+        <v>460582</v>
       </c>
       <c r="R11" t="n">
-        <v>7086783</v>
+        <v>7086692</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1852,7 +1887,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1862,7 +1897,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1914,10 +1949,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123987918</v>
+        <v>123988808</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>95335</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1926,25 +1961,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1954,13 +1989,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>460582</v>
+        <v>460285</v>
       </c>
       <c r="R12" t="n">
-        <v>7086692</v>
+        <v>7086685</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1987,21 +2022,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>09:02</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>09:02</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2010,41 +2035,16 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -3090,10 +3090,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123988446</v>
+        <v>123988915</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3106,34 +3106,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>460371</v>
+        <v>460262</v>
       </c>
       <c r="R21" t="n">
-        <v>7086703</v>
+        <v>7086681</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -3192,7 +3192,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123989420</v>
+        <v>123988446</v>
       </c>
       <c r="B22" t="n">
         <v>78810</v>
@@ -3228,14 +3228,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>460223</v>
+        <v>460371</v>
       </c>
       <c r="R22" t="n">
-        <v>7086707</v>
+        <v>7086703</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3294,10 +3294,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123988915</v>
+        <v>123989420</v>
       </c>
       <c r="B23" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3310,21 +3310,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>460262</v>
+        <v>460223</v>
       </c>
       <c r="R23" t="n">
-        <v>7086681</v>
+        <v>7086707</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>

--- a/artfynd/A 60117-2024 artfynd.xlsx
+++ b/artfynd/A 60117-2024 artfynd.xlsx
@@ -3635,7 +3635,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124025469</v>
+        <v>124025462</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3675,10 +3675,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>460378</v>
+        <v>460183</v>
       </c>
       <c r="R26" t="n">
-        <v>7086700</v>
+        <v>7086654</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack Färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3742,7 +3742,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124025459</v>
+        <v>124025456</v>
       </c>
       <c r="B27" t="n">
         <v>57513</v>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>460150</v>
+        <v>460284</v>
       </c>
       <c r="R27" t="n">
-        <v>7086691</v>
+        <v>7086765</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3849,7 +3849,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124025456</v>
+        <v>124025467</v>
       </c>
       <c r="B28" t="n">
         <v>57513</v>
@@ -3889,10 +3889,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>460284</v>
+        <v>460343</v>
       </c>
       <c r="R28" t="n">
-        <v>7086765</v>
+        <v>7086730</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3956,10 +3956,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124025476</v>
+        <v>124025470</v>
       </c>
       <c r="B29" t="n">
-        <v>91030</v>
+        <v>91705</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3968,25 +3968,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>67</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3996,10 +3996,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>460154</v>
+        <v>460140</v>
       </c>
       <c r="R29" t="n">
-        <v>7086694</v>
+        <v>7086711</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4040,7 +4040,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4059,10 +4058,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124025475</v>
+        <v>124025453</v>
       </c>
       <c r="B30" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4075,21 +4074,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4099,10 +4098,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>460284</v>
+        <v>460668</v>
       </c>
       <c r="R30" t="n">
-        <v>7086722</v>
+        <v>7086736</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4135,6 +4134,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4161,7 +4165,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124025467</v>
+        <v>124025458</v>
       </c>
       <c r="B31" t="n">
         <v>57513</v>
@@ -4201,10 +4205,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>460343</v>
+        <v>460205</v>
       </c>
       <c r="R31" t="n">
-        <v>7086730</v>
+        <v>7086746</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4370,7 +4374,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124025453</v>
+        <v>124025459</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -4410,10 +4414,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>460668</v>
+        <v>460150</v>
       </c>
       <c r="R33" t="n">
-        <v>7086736</v>
+        <v>7086691</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4477,7 +4481,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124025462</v>
+        <v>124025465</v>
       </c>
       <c r="B34" t="n">
         <v>57513</v>
@@ -4517,10 +4521,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>460183</v>
+        <v>460240</v>
       </c>
       <c r="R34" t="n">
-        <v>7086654</v>
+        <v>7086700</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4584,7 +4588,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124025461</v>
+        <v>124025460</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -4624,10 +4628,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>460078</v>
+        <v>460124</v>
       </c>
       <c r="R35" t="n">
-        <v>7086651</v>
+        <v>7086694</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4664,7 +4668,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4691,10 +4695,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124025465</v>
+        <v>124025475</v>
       </c>
       <c r="B36" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4707,21 +4711,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4731,10 +4735,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>460240</v>
+        <v>460284</v>
       </c>
       <c r="R36" t="n">
-        <v>7086700</v>
+        <v>7086722</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4767,11 +4771,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4798,7 +4797,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124025457</v>
+        <v>124025469</v>
       </c>
       <c r="B37" t="n">
         <v>57513</v>
@@ -4838,10 +4837,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>460222</v>
+        <v>460378</v>
       </c>
       <c r="R37" t="n">
-        <v>7086760</v>
+        <v>7086700</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4878,7 +4877,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack Färska och äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4905,7 +4904,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124025458</v>
+        <v>124025464</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -4945,10 +4944,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>460205</v>
+        <v>460209</v>
       </c>
       <c r="R38" t="n">
-        <v>7086746</v>
+        <v>7086674</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5012,7 +5011,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124025460</v>
+        <v>124025461</v>
       </c>
       <c r="B39" t="n">
         <v>57513</v>
@@ -5052,10 +5051,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>460124</v>
+        <v>460078</v>
       </c>
       <c r="R39" t="n">
-        <v>7086694</v>
+        <v>7086651</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5092,7 +5091,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5119,7 +5118,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124025464</v>
+        <v>124025457</v>
       </c>
       <c r="B40" t="n">
         <v>57513</v>
@@ -5159,10 +5158,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>460209</v>
+        <v>460222</v>
       </c>
       <c r="R40" t="n">
-        <v>7086674</v>
+        <v>7086760</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5199,7 +5198,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5226,10 +5225,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124025470</v>
+        <v>124025476</v>
       </c>
       <c r="B41" t="n">
-        <v>91705</v>
+        <v>91030</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5238,25 +5237,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>67</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5266,10 +5265,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>460140</v>
+        <v>460154</v>
       </c>
       <c r="R41" t="n">
-        <v>7086711</v>
+        <v>7086694</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5310,6 +5309,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60117-2024 artfynd.xlsx
+++ b/artfynd/A 60117-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123990224</v>
+        <v>124025470</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>67</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Häggsjövik V, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460370</v>
+        <v>460140</v>
       </c>
       <c r="R2" t="n">
-        <v>7086712</v>
+        <v>7086711</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123987913</v>
+        <v>123988915</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460590</v>
+        <v>460262</v>
       </c>
       <c r="R3" t="n">
-        <v>7086691</v>
+        <v>7086681</v>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123991060</v>
+        <v>123989081</v>
       </c>
       <c r="B4" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,42 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460261</v>
+        <v>460222</v>
       </c>
       <c r="R4" t="n">
-        <v>7086790</v>
+        <v>7086704</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,21 +937,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -980,56 +950,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123990830</v>
+        <v>123987913</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,47 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460249</v>
+        <v>460590</v>
       </c>
       <c r="R5" t="n">
-        <v>7086743</v>
+        <v>7086691</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,26 +1034,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på en gran.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1132,94 +1047,64 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123990841</v>
+        <v>123988808</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>2809</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460642</v>
+        <v>460285</v>
       </c>
       <c r="R6" t="n">
-        <v>7086699</v>
+        <v>7086685</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1275,72 +1160,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123988447</v>
+        <v>123987918</v>
       </c>
       <c r="B7" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460385</v>
+        <v>460582</v>
       </c>
       <c r="R7" t="n">
-        <v>7086719</v>
+        <v>7086692</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1369,7 +1230,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1379,7 +1240,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1394,6 +1255,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1411,58 +1292,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123989562</v>
+        <v>123988446</v>
       </c>
       <c r="B8" t="n">
-        <v>56714</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460190</v>
+        <v>460371</v>
       </c>
       <c r="R8" t="n">
-        <v>7086684</v>
+        <v>7086703</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1489,26 +1360,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:46</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färsk spillning ovanpå snötäcket i flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1517,40 +1373,30 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123988998</v>
+        <v>123988501</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1574,14 +1420,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460216</v>
+        <v>460349</v>
       </c>
       <c r="R9" t="n">
-        <v>7086687</v>
+        <v>7086748</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1613,7 +1459,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1623,7 +1469,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1675,19 +1521,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123991344</v>
+        <v>123988998</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1711,17 +1552,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460415</v>
+        <v>460216</v>
       </c>
       <c r="R10" t="n">
-        <v>7086783</v>
+        <v>7086687</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1750,7 +1591,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1760,7 +1601,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1812,19 +1653,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123987918</v>
+        <v>123989420</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1848,17 +1684,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460582</v>
+        <v>460223</v>
       </c>
       <c r="R11" t="n">
-        <v>7086692</v>
+        <v>7086707</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1885,21 +1721,11 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:02</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:02</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1908,91 +1734,61 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123988808</v>
+        <v>123989913</v>
       </c>
       <c r="B12" t="n">
-        <v>95335</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>460285</v>
+        <v>460291</v>
       </c>
       <c r="R12" t="n">
-        <v>7086685</v>
+        <v>7086773</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -2051,19 +1847,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123989913</v>
+        <v>123990224</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2087,14 +1878,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460291</v>
+        <v>460370</v>
       </c>
       <c r="R13" t="n">
-        <v>7086773</v>
+        <v>7086712</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2156,16 +1947,11 @@
         <v>123990278</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2290,58 +2076,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123989782</v>
+        <v>123990849</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460153</v>
+        <v>460241</v>
       </c>
       <c r="R15" t="n">
-        <v>7086693</v>
+        <v>7086734</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2370,7 +2146,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2380,12 +2156,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en stående och en liggande död granstam.</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2414,12 +2185,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2437,19 +2208,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123991476</v>
+        <v>123991344</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2477,13 +2243,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460544</v>
+        <v>460415</v>
       </c>
       <c r="R16" t="n">
-        <v>7086749</v>
+        <v>7086783</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2512,7 +2278,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2522,12 +2288,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2579,72 +2340,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123991224</v>
+        <v>123991476</v>
       </c>
       <c r="B17" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
+          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>460332</v>
+        <v>460544</v>
       </c>
       <c r="R17" t="n">
-        <v>7086777</v>
+        <v>7086749</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2673,7 +2410,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2683,7 +2420,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2698,6 +2440,26 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2715,32 +2477,27 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123990384</v>
+        <v>123989782</v>
       </c>
       <c r="B18" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2748,24 +2505,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2774,13 +2517,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>460150</v>
+        <v>460153</v>
       </c>
       <c r="R18" t="n">
-        <v>7086698</v>
+        <v>7086693</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2809,7 +2552,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2819,7 +2562,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en stående och en liggande död granstam.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2834,6 +2582,26 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2851,15 +2619,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123990849</v>
+        <v>123990393</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2867,37 +2630,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>460241</v>
+        <v>460414</v>
       </c>
       <c r="R19" t="n">
-        <v>7086734</v>
+        <v>7086730</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2924,19 +2692,14 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>10:22</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2947,56 +2710,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123989081</v>
+        <v>123990830</v>
       </c>
       <c r="B20" t="n">
-        <v>91008</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3004,37 +2737,47 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>460222</v>
+        <v>460249</v>
       </c>
       <c r="R20" t="n">
-        <v>7086704</v>
+        <v>7086743</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3061,11 +2804,26 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på en gran.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3074,31 +2832,51 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123988915</v>
+        <v>124025453</v>
       </c>
       <c r="B21" t="n">
-        <v>91008</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3106,37 +2884,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Häggsjövik V, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>460262</v>
+        <v>460668</v>
       </c>
       <c r="R21" t="n">
-        <v>7086681</v>
+        <v>7086736</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3166,6 +2944,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3180,27 +2963,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123988446</v>
+        <v>124025456</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3208,37 +2986,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Häggsjövik V, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>460371</v>
+        <v>460284</v>
       </c>
       <c r="R22" t="n">
-        <v>7086703</v>
+        <v>7086765</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3268,6 +3046,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3282,27 +3065,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123989420</v>
+        <v>124025457</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3310,37 +3088,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
+          <t>Häggsjövik V, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>460223</v>
+        <v>460222</v>
       </c>
       <c r="R23" t="n">
-        <v>7086707</v>
+        <v>7086760</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3370,6 +3148,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3384,27 +3167,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123988501</v>
+        <v>124025458</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3412,37 +3190,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Häggsjövik V, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>460349</v>
+        <v>460205</v>
       </c>
       <c r="R24" t="n">
-        <v>7086748</v>
+        <v>7086746</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3469,19 +3247,14 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>09:24</t>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3492,56 +3265,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123988472</v>
+        <v>124025459</v>
       </c>
       <c r="B25" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3549,37 +3292,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lill-Pottmyren, Lill-Pottmyren, Jmt</t>
+          <t>Häggsjövik V, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>460371</v>
+        <v>460150</v>
       </c>
       <c r="R25" t="n">
-        <v>7086703</v>
+        <v>7086691</v>
       </c>
       <c r="S25" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3609,6 +3352,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3623,27 +3371,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124025462</v>
+        <v>124025460</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3675,10 +3418,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>460183</v>
+        <v>460124</v>
       </c>
       <c r="R26" t="n">
-        <v>7086654</v>
+        <v>7086694</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3742,15 +3485,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124025456</v>
+        <v>124025461</v>
       </c>
       <c r="B27" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3782,10 +3520,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>460284</v>
+        <v>460078</v>
       </c>
       <c r="R27" t="n">
-        <v>7086765</v>
+        <v>7086651</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3822,7 +3560,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3849,15 +3587,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124025467</v>
+        <v>124025462</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3889,10 +3622,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>460343</v>
+        <v>460183</v>
       </c>
       <c r="R28" t="n">
-        <v>7086730</v>
+        <v>7086654</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3956,37 +3689,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124025470</v>
+        <v>124025464</v>
       </c>
       <c r="B29" t="n">
-        <v>91705</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3996,10 +3724,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>460140</v>
+        <v>460209</v>
       </c>
       <c r="R29" t="n">
-        <v>7086711</v>
+        <v>7086674</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4032,6 +3760,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4058,15 +3791,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124025453</v>
+        <v>124025465</v>
       </c>
       <c r="B30" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4098,10 +3826,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>460668</v>
+        <v>460240</v>
       </c>
       <c r="R30" t="n">
-        <v>7086736</v>
+        <v>7086700</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4165,15 +3893,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124025458</v>
+        <v>124025467</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4205,10 +3928,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>460205</v>
+        <v>460343</v>
       </c>
       <c r="R31" t="n">
-        <v>7086746</v>
+        <v>7086730</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4272,15 +3995,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124025473</v>
+        <v>124025469</v>
       </c>
       <c r="B32" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4288,21 +4006,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4312,10 +4030,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>460235</v>
+        <v>460378</v>
       </c>
       <c r="R32" t="n">
-        <v>7086681</v>
+        <v>7086700</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4348,6 +4066,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack Färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4374,32 +4097,27 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124025459</v>
+        <v>123989562</v>
       </c>
       <c r="B33" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4408,19 +4126,24 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Häggsjövik V, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>460150</v>
+        <v>460190</v>
       </c>
       <c r="R33" t="n">
-        <v>7086691</v>
+        <v>7086684</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4447,14 +4170,24 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Färsk spillning ovanpå snötäcket i flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4465,48 +4198,48 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124025465</v>
+        <v>123988447</v>
       </c>
       <c r="B34" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4514,20 +4247,39 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Häggsjövik V, Jmt</t>
+          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>460240</v>
+        <v>460385</v>
       </c>
       <c r="R34" t="n">
-        <v>7086700</v>
+        <v>7086719</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4554,14 +4306,19 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4572,48 +4329,48 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124025460</v>
+        <v>123990384</v>
       </c>
       <c r="B35" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4621,17 +4378,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Häggsjövik V, Jmt</t>
+          <t>Östra Fisktjärnen, Östra Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>460124</v>
+        <v>460150</v>
       </c>
       <c r="R35" t="n">
-        <v>7086694</v>
+        <v>7086698</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4661,14 +4437,19 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4679,66 +4460,85 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124025475</v>
+        <v>123991224</v>
       </c>
       <c r="B36" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Häggsjövik V, Jmt</t>
+          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>460284</v>
+        <v>460332</v>
       </c>
       <c r="R36" t="n">
-        <v>7086722</v>
+        <v>7086777</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4768,11 +4568,21 @@
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-04-12</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4781,31 +4591,31 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124025469</v>
+        <v>123988564</v>
       </c>
       <c r="B37" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4813,37 +4623,46 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Häggsjövik V, Jmt</t>
+          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>460378</v>
+        <v>460318</v>
       </c>
       <c r="R37" t="n">
-        <v>7086700</v>
+        <v>7086671</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4873,11 +4692,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack Färska och äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4892,27 +4706,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124025464</v>
+        <v>123990841</v>
       </c>
       <c r="B38" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4920,34 +4729,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Häggsjövik V, Jmt</t>
+          <t>Häggsjövik, Hotagen, Häggsjövik, Hotagen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>460209</v>
+        <v>460642</v>
       </c>
       <c r="R38" t="n">
-        <v>7086674</v>
+        <v>7086699</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4982,11 +4791,6 @@
           <t>2025-04-12</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4999,332 +4803,15 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>124025461</v>
-      </c>
-      <c r="B39" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Häggsjövik V, Jmt</t>
-        </is>
-      </c>
-      <c r="Q39" t="n">
-        <v>460078</v>
-      </c>
-      <c r="R39" t="n">
-        <v>7086651</v>
-      </c>
-      <c r="S39" t="n">
-        <v>10</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
-      <c r="AD39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>124025457</v>
-      </c>
-      <c r="B40" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Häggsjövik V, Jmt</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>460222</v>
-      </c>
-      <c r="R40" t="n">
-        <v>7086760</v>
-      </c>
-      <c r="S40" t="n">
-        <v>10</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>124025476</v>
-      </c>
-      <c r="B41" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Häggsjövik V, Jmt</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>460154</v>
-      </c>
-      <c r="R41" t="n">
-        <v>7086694</v>
-      </c>
-      <c r="S41" t="n">
-        <v>10</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF41" t="inlineStr"/>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60117-2024 artfynd.xlsx
+++ b/artfynd/A 60117-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124025470</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123988915</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123989081</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123987913</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123988808</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1289,6 +1319,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123987918</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123988446</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1518,6 +1558,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123988501</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1650,6 +1695,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123988998</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1747,6 +1797,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123989420</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1844,6 +1899,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123989913</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1941,6 +2001,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123990224</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2073,6 +2138,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123990278</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2205,6 +2275,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123990849</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2337,6 +2412,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123991344</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2474,6 +2554,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123991476</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2616,6 +2701,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123989782</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2723,6 +2813,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123990393</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2870,6 +2965,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123990830</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2972,6 +3072,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124025453</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3074,6 +3179,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124025456</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3176,6 +3286,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124025457</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3278,6 +3393,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124025458</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3380,6 +3500,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124025459</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3482,6 +3607,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124025460</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3584,6 +3714,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124025461</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3686,6 +3821,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124025462</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3788,6 +3928,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124025464</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3890,6 +4035,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124025465</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3992,6 +4142,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124025467</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4094,6 +4249,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124025469</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4216,6 +4376,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123989562</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4347,6 +4512,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123988447</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4478,6 +4648,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123990384</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4609,6 +4784,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123991224</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4715,6 +4895,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123988564</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4812,8 +4997,52 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123990841</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>